--- a/Demo_W1_W2/Archivio_Cicli/Cicli/2026Q4/Schede_2026Q4.xlsx
+++ b/Demo_W1_W2/Archivio_Cicli/Cicli/2026Q4/Schede_2026Q4.xlsx
@@ -9,17 +9,17 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indice" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-01" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-07" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-12" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-02" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-02" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-07" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-12" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-03" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-05" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-06" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-10" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-13" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-09" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-04" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-11" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-09" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-04" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-11" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-16" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NFR-08" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
@@ -30,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -153,13 +153,8 @@
     <font>
       <sz val="9.5"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00595959"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -192,8 +187,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -204,8 +199,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-        <bgColor rgb="00D9D9D9"/>
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -296,6 +291,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +466,10 @@
     <xf numFmtId="0" fontId="17" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -474,14 +478,13 @@
     <xf numFmtId="0" fontId="17" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -926,6 +929,119 @@
           <order val="0"/>
           <tx>
             <strRef>
+              <f>'NFR-16'!F27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLblPos val="t"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'NFR-16'!$A$28:$A$29</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'NFR-16'!$F$28:$F$29</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="5"/>
+          <min val="1"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="1"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Score composito per trimestre (scala fissa 1-5)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
               <f>'NFR-08'!F27</f>
             </strRef>
           </tx>
@@ -1039,6 +1155,119 @@
           <order val="0"/>
           <tx>
             <strRef>
+              <f>'NFR-02'!F27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="7"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="1F3864"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLblPos val="t"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'NFR-02'!$A$28:$A$32</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'NFR-02'!$F$28:$F$32</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="5"/>
+          <min val="1"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+        <majorUnit val="1"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Score composito per trimestre (scala fissa 1-5)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
               <f>'NFR-07'!F27</f>
             </strRef>
           </tx>
@@ -1125,7 +1354,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -1191,119 +1420,6 @@
           <val>
             <numRef>
               <f>'NFR-12'!$F$28:$F$32</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-          <max val="5"/>
-          <min val="1"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-        <majorUnit val="1"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:noFill/>
-      <a:prstDash val="solid"/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Score composito per trimestre (scala fissa 1-5)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'NFR-02'!F27</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="1F3864"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="7"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="1F3864"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="1"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-          </dLbls>
-          <cat>
-            <numRef>
-              <f>'NFR-02'!$A$28:$A$32</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'NFR-02'!$F$28:$F$32</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2003,6 +2119,33 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3960000" cy="1980000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
       <row>33</row>
       <rowOff>0</rowOff>
     </from>
@@ -2642,20 +2785,20 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>NFR-07</t>
+          <t>NFR-02</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>Ransomware presso un fornitore di servizi di pagamento  ◆</t>
+          <t>Concentrazione su un fornitore cloud critico  ◆</t>
         </is>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Entro l'anno</t>
+          <t>Margine 1 anno</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -2665,7 +2808,7 @@
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>Confermato</t>
+          <t>Variato</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -2680,18 +2823,18 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>NFR-12</t>
+          <t>NFR-07</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>Errori operativi nei pagamenti istantanei obbligatori</t>
+          <t>Ransomware presso un fornitore di servizi di pagamento  ◆</t>
         </is>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="E7" s="11" t="inlineStr">
+        <v>3.75</v>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Entro l'anno</t>
         </is>
@@ -2708,7 +2851,7 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>Funzione Operations</t>
+          <t>Funzione ICT &amp; Security Risk</t>
         </is>
       </c>
     </row>
@@ -2718,25 +2861,25 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>NFR-02</t>
+          <t>NFR-12</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>Concentrazione su un fornitore cloud critico  ◆</t>
+          <t>Errori operativi nei pagamenti istantanei obbligatori</t>
         </is>
       </c>
       <c r="D8" s="7" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>Margine 1 anno</t>
-        </is>
-      </c>
-      <c r="F8" s="14" t="inlineStr">
-        <is>
-          <t>Monitoraggio</t>
+          <t>Entro l'anno</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>Attenzione</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
@@ -2746,7 +2889,7 @@
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
-          <t>Funzione ICT &amp; Security Risk</t>
+          <t>Funzione Operations</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2910,7 @@
       <c r="D9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="11" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Entro l'anno</t>
         </is>
@@ -2805,7 +2948,7 @@
       <c r="D10" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="13" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>Margine 1 anno</t>
         </is>
@@ -2843,7 +2986,7 @@
       <c r="D11" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Entro l'anno</t>
         </is>
@@ -2881,7 +3024,7 @@
       <c r="D12" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="13" t="inlineStr">
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>Margine 1 anno</t>
         </is>
@@ -2908,20 +3051,20 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>NFR-13</t>
+          <t>NFR-09</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Vertenze e carenza di competenze in funzioni IT critiche</t>
+          <t>Violazione di sanzioni internazionali tramite triangolazioni  ◆</t>
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Entro l'anno</t>
+          <t>Margine 1,3 anni</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -2931,12 +3074,12 @@
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Nuovo</t>
+          <t>Confermato</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>Da assegnare</t>
+          <t>Funzione Compliance</t>
         </is>
       </c>
     </row>
@@ -2946,25 +3089,25 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>NFR-09</t>
+          <t>NFR-04</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Violazione di sanzioni internazionali tramite triangolazioni  ◆</t>
+          <t>Eventi climatici estremi su sedi e data center</t>
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>Margine 1,3 anni</t>
-        </is>
-      </c>
-      <c r="F14" s="14" t="inlineStr">
-        <is>
-          <t>Monitoraggio</t>
+          <t>Entro l'anno</t>
+        </is>
+      </c>
+      <c r="F14" s="12" t="inlineStr">
+        <is>
+          <t>Attenzione</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -2974,7 +3117,7 @@
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
-          <t>Funzione Compliance</t>
+          <t>Funzione Business Continuity</t>
         </is>
       </c>
     </row>
@@ -2984,25 +3127,25 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>NFR-04</t>
+          <t>NFR-11</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Eventi climatici estremi su sedi e data center</t>
+          <t>Fine del supporto dei sistemi di pagamento legacy</t>
         </is>
       </c>
       <c r="D15" s="7" t="n">
         <v>2.8</v>
       </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Entro l'anno</t>
-        </is>
-      </c>
-      <c r="F15" s="12" t="inlineStr">
-        <is>
-          <t>Attenzione</t>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>AGIRE ORA</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Attivazione</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -3012,7 +3155,7 @@
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
-          <t>Funzione Business Continuity</t>
+          <t>Funzione IT Operations</t>
         </is>
       </c>
     </row>
@@ -3022,35 +3165,35 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>NFR-11</t>
+          <t>NFR-16</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>Fine del supporto dei sistemi di pagamento legacy</t>
+          <t>Vertenze e carenza di tecnici nei ruoli IT critici</t>
         </is>
       </c>
       <c r="D16" s="7" t="n">
         <v>2.8</v>
       </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>AGIRE ORA</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>Attivazione</t>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>Margine 1,8 anni</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>Monitoraggio</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Confermato</t>
+          <t>Variato</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>Funzione IT Operations</t>
+          <t>Da assegnare</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3214,7 @@
       <c r="D17" s="7" t="n">
         <v>2.75</v>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Margine 1 anno</t>
         </is>
@@ -3139,751 +3282,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H50"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>Horizon Scan NFR — schede dei rischi · ciclo 2026Q4 · dati al 31/12/2026 · validato · Uso interno</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>9 · NFR-13 · Vertenze e carenza di competenze in funzioni IT critiche</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="n"/>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="18" t="n"/>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="19" t="inlineStr">
-        <is>
-          <t>score 3,00   nuovo   ·   Entro l'anno   ·   Monitoraggio</t>
-        </is>
-      </c>
-      <c r="H2" s="18" t="n"/>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>L1-03 · Rapporti di impiego e sicurezza sul lavoro</t>
-        </is>
-      </c>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>Driver: DRV-HUM</t>
-        </is>
-      </c>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>Owner: Da assegnare · Presidio: Non verificato</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="n"/>
-      <c r="G3" s="20" t="n"/>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>Esito: Nuovo · validato</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>Il rischio</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="24" t="n"/>
-      <c r="H5" s="24" t="n"/>
-    </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>Scioperi di settore e uscite di personale tecnico non rimpiazzabile che lasciano scoperti ruoli IT critici, con violazioni di obblighi di lavoro e sicurezza nei turni di copertura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>Razionale: il fenomeno in termini di rischio</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="n"/>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="24" t="n"/>
-      <c r="H8" s="24" t="n"/>
-    </row>
-    <row r="9" ht="46.5" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>La vertenza nazionale del settore e le uscite di tecnici difficili da sostituire (causa) lasciano scoperti ruoli IT critici durante scioperi o dimissioni, con turni di copertura che violano obblighi di lavoro e sicurezza (evento); processi critici si degradano e la Banca rischia vertenze e sanzioni (danno). Rischio nuovo: nessun rischio del registro copriva i rapporti di impiego (L1-03).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>Valutazione, dimensione per dimensione (valori validati)</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="24" t="n"/>
-      <c r="H11" s="24" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>Dimensione</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>Valore</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>Perche' questo valore: informazioni e documenti</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="33" customHeight="1">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>Impatto</t>
-        </is>
-      </c>
-      <c r="B13" s="55" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="29" t="inlineStr">
-        <is>
-          <t>Rilevante. Durante le astensioni si degradano processi critici che dipendono da pochi tecnici (Piano di successione dei ruoli IT critici, Direzione Risorse Umane).</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="33" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>Probabilita</t>
-        </is>
-      </c>
-      <c r="B14" s="55" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="29" t="inlineStr">
-        <is>
-          <t>Possibile. Lo sciopero nazionale del personale bancario e la carenza di tecnici IT sono in corso nel settore; la Banca e' esposta perche' il Piano di successione copre solo una parte dei ruoli.</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>Prossimita</t>
-        </is>
-      </c>
-      <c r="B15" s="55" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="29" t="inlineStr">
-        <is>
-          <t>Da uno a due anni. La vertenza e' in corso nel settore, senza astensioni annunciate presso la Banca.</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>Velocity</t>
-        </is>
-      </c>
-      <c r="B16" s="55" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>Da tre a sei mesi. Le uscite di personale e i periodi di vertenza si sviluppano in alcuni mesi (Sciopero nazionale del personale bancario).</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>Score composito 3,00 = (0,35 x 3 + 0,25 x 3 + 0,20 x 3 + 0,20 x 3) / 1,00. La rilevanza delle fonti e' nella tabella Fonti.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
-        <is>
-          <t>Urgenza (disuguaglianza di Mosca) e livello di allerta</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="24" t="n"/>
-      <c r="H19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
-        <is>
-          <t>Livello di allerta: Monitoraggio — nessun segnale forte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>Agire entro l'anno. Tempo necessario X + Y = 0,25 + 0,50 = 0,75 anni; tempo disponibile Z = 1,5 anni (Prossimita 3). Margine Z - (X + Y) = 0,75.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>Cosa e' cambiato nel ciclo</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="n"/>
-      <c r="C23" s="24" t="n"/>
-      <c r="D23" s="24" t="n"/>
-      <c r="E23" s="24" t="n"/>
-      <c r="F23" s="24" t="n"/>
-      <c r="G23" s="24" t="n"/>
-      <c r="H23" s="24" t="n"/>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>Rischio nuovo nel ciclo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>Andamento negli ultimi trimestri</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="24" t="n"/>
-      <c r="F26" s="24" t="n"/>
-      <c r="G26" s="24" t="n"/>
-      <c r="H26" s="24" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="33" t="inlineStr">
-        <is>
-          <t>Ciclo</t>
-        </is>
-      </c>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t>Imp</t>
-        </is>
-      </c>
-      <c r="C27" s="33" t="inlineStr">
-        <is>
-          <t>Prob</t>
-        </is>
-      </c>
-      <c r="D27" s="33" t="inlineStr">
-        <is>
-          <t>Pross</t>
-        </is>
-      </c>
-      <c r="E27" s="33" t="inlineStr">
-        <is>
-          <t>Vel</t>
-        </is>
-      </c>
-      <c r="F27" s="33" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="34" t="inlineStr">
-        <is>
-          <t>2026Q4</t>
-        </is>
-      </c>
-      <c r="B28" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="F28" s="37" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="62" t="inlineStr">
-        <is>
-          <t>Rischio entrato nel registro nel 2026Q4: l'andamento si vedra' dal prossimo ciclo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="23" t="inlineStr">
-        <is>
-          <t>Fonti</t>
-        </is>
-      </c>
-      <c r="B31" s="24" t="n"/>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="24" t="n"/>
-      <c r="F31" s="24" t="n"/>
-      <c r="G31" s="24" t="n"/>
-      <c r="H31" s="24" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="26" t="inlineStr">
-        <is>
-          <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D32" s="26" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="E32" s="26" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="F32" s="26" t="inlineStr">
-        <is>
-          <t>Rilevanza</t>
-        </is>
-      </c>
-      <c r="G32" s="26" t="n"/>
-    </row>
-    <row r="33" ht="32" customHeight="1">
-      <c r="A33" s="39" t="inlineStr">
-        <is>
-          <t>Sciopero nazionale del personale bancario e carenza di tecnici IT</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="40" t="inlineStr">
-        <is>
-          <t>06/10/2026</t>
-        </is>
-      </c>
-      <c r="E33" s="43" t="inlineStr">
-        <is>
-          <t>Esterna</t>
-        </is>
-      </c>
-      <c r="F33" s="44" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G33" s="39" t="n"/>
-      <c r="H33" s="6" t="n"/>
-    </row>
-    <row r="34" ht="32" customHeight="1">
-      <c r="A34" s="39" t="inlineStr">
-        <is>
-          <t>Piano di successione dei ruoli IT critici — Direzione Risorse Umane</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="40" t="inlineStr">
-        <is>
-          <t>15/11/2026</t>
-        </is>
-      </c>
-      <c r="E34" s="41" t="inlineStr">
-        <is>
-          <t>Interna</t>
-        </is>
-      </c>
-      <c r="F34" s="42" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="G34" s="39" t="n"/>
-      <c r="H34" s="6" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="23" t="inlineStr">
-        <is>
-          <t>Azioni</t>
-        </is>
-      </c>
-      <c r="B36" s="24" t="n"/>
-      <c r="C36" s="24" t="n"/>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="24" t="n"/>
-      <c r="F36" s="24" t="n"/>
-      <c r="G36" s="24" t="n"/>
-      <c r="H36" s="24" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="26" t="inlineStr">
-        <is>
-          <t>Azione</t>
-        </is>
-      </c>
-      <c r="F37" s="26" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="H37" s="26" t="inlineStr">
-        <is>
-          <t>Orizzonte · stato</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="18.5" customHeight="1">
-      <c r="A38" s="45" t="inlineStr">
-        <is>
-          <t>• Estendere il piano di successione a tutti i ruoli IT critici, con backup formati.</t>
-        </is>
-      </c>
-      <c r="F38" s="46" t="inlineStr">
-        <is>
-          <t>Direzione Risorse Umane</t>
-        </is>
-      </c>
-      <c r="H38" s="46" t="inlineStr">
-        <is>
-          <t>6 mesi · Approvata (ciclo 2026Q4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="32" customHeight="1">
-      <c r="A39" s="47" t="inlineStr">
-        <is>
-          <t>Perche': Oggi il Piano di successione copre circa meta' dei ruoli critici: e' la lacuna principale del rischio.</t>
-        </is>
-      </c>
-      <c r="B39" s="48" t="n"/>
-      <c r="C39" s="48" t="n"/>
-      <c r="D39" s="48" t="n"/>
-      <c r="E39" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: Ogni ruolo critico con un sostituto formato; i ruoli senza sostituto (KRI di esposizione) devono scendere sotto la soglia di attenzione.</t>
-        </is>
-      </c>
-      <c r="F39" s="48" t="n"/>
-      <c r="G39" s="48" t="n"/>
-      <c r="H39" s="48" t="n"/>
-    </row>
-    <row r="40" ht="18.5" customHeight="1">
-      <c r="A40" s="45" t="inlineStr">
-        <is>
-          <t>• Definire i servizi minimi IT garantiti in caso di sciopero, d'intesa con le rappresentanze.</t>
-        </is>
-      </c>
-      <c r="F40" s="46" t="inlineStr">
-        <is>
-          <t>Direzione Sistemi Informativi</t>
-        </is>
-      </c>
-      <c r="H40" s="46" t="inlineStr">
-        <is>
-          <t>3 mesi · Approvata (ciclo 2026Q4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="32" customHeight="1">
-      <c r="A41" s="47" t="inlineStr">
-        <is>
-          <t>Perche': Senza servizi minimi concordati un'astensione puo' fermare processi critici o imporre turni non conformi.</t>
-        </is>
-      </c>
-      <c r="B41" s="48" t="n"/>
-      <c r="C41" s="48" t="n"/>
-      <c r="D41" s="48" t="n"/>
-      <c r="E41" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: Un danno minore in caso di sciopero (Impatto) e turni di copertura conformi agli obblighi di lavoro.</t>
-        </is>
-      </c>
-      <c r="F41" s="48" t="n"/>
-      <c r="G41" s="48" t="n"/>
-      <c r="H41" s="48" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="23" t="inlineStr">
-        <is>
-          <t>KRI in vigore</t>
-        </is>
-      </c>
-      <c r="B43" s="24" t="n"/>
-      <c r="C43" s="24" t="n"/>
-      <c r="D43" s="24" t="n"/>
-      <c r="E43" s="24" t="n"/>
-      <c r="F43" s="24" t="n"/>
-      <c r="G43" s="24" t="n"/>
-      <c r="H43" s="24" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="49" t="inlineStr">
-        <is>
-          <t>Indicatore</t>
-        </is>
-      </c>
-      <c r="E44" s="49" t="inlineStr">
-        <is>
-          <t>Valore</t>
-        </is>
-      </c>
-      <c r="F44" s="49" t="inlineStr">
-        <is>
-          <t>Soglie (attenzione / allerta)</t>
-        </is>
-      </c>
-      <c r="G44" s="49" t="inlineStr">
-        <is>
-          <t>Ciclo prima</t>
-        </is>
-      </c>
-      <c r="H44" s="49" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="50" t="inlineStr">
-        <is>
-          <t>[Esposizione] Ruoli IT critici senza sostituto formato (n)</t>
-        </is>
-      </c>
-      <c r="E45" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F45" s="52" t="inlineStr">
-        <is>
-          <t>3,0 / 6,0</t>
-        </is>
-      </c>
-      <c r="G45" s="52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="63" t="inlineStr">
-        <is>
-          <t>Non rilevato</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="32" customHeight="1">
-      <c r="A46" s="47" t="inlineStr">
-        <is>
-          <t>Perche' lo misuriamo: Misura quanto la Banca e' esposta: ogni ruolo critico senza sostituto e' un punto di blocco.</t>
-        </is>
-      </c>
-      <c r="B46" s="48" t="n"/>
-      <c r="C46" s="48" t="n"/>
-      <c r="D46" s="48" t="n"/>
-      <c r="E46" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: In calo con l'estensione del piano di successione, fino a zero.</t>
-        </is>
-      </c>
-      <c r="F46" s="48" t="n"/>
-      <c r="G46" s="48" t="n"/>
-      <c r="H46" s="48" t="n"/>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="50" t="inlineStr">
-        <is>
-          <t>[Evoluzione] Turnover volontario annualizzato del personale IT (%)</t>
-        </is>
-      </c>
-      <c r="E47" s="51" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F47" s="52" t="inlineStr">
-        <is>
-          <t>8,0 / 12,0</t>
-        </is>
-      </c>
-      <c r="G47" s="52" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="63" t="inlineStr">
-        <is>
-          <t>Non rilevato</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="32" customHeight="1">
-      <c r="A48" s="47" t="inlineStr">
-        <is>
-          <t>Perche' lo misuriamo: Misura quanto cresce la perdita di competenze tecniche.</t>
-        </is>
-      </c>
-      <c r="B48" s="48" t="n"/>
-      <c r="C48" s="48" t="n"/>
-      <c r="D48" s="48" t="n"/>
-      <c r="E48" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: Stabile sotto la soglia di attenzione; oltre la soglia di allerta il rischio si avvicina e la Prossimita' va rivista.</t>
-        </is>
-      </c>
-      <c r="F48" s="48" t="n"/>
-      <c r="G48" s="48" t="n"/>
-      <c r="H48" s="48" t="n"/>
-    </row>
-    <row r="50" ht="61" customHeight="1">
-      <c r="A50" s="15" t="inlineStr">
-        <is>
-          <t>Legenda — Imp = Impatto, Prob = Probabilita, Pross = Prossimita, Vel = Velocity (1-5, 5 = peggiore; n.v. = non valutata, nessuna fonte ne documenta i tempi). Rilevanza di una fonte per la previsione: Alta = fonte primaria o caso documentato, Media = fonte specializzata, Bassa = generalista. Presidio = giudizio della Banca sui controlli, fuori dallo score. X = anni per decidere e avviare la mitigazione; Y = anni per mitigare (azioni o adeguamento strutturale); Z = anni prima che il rischio possa manifestarsi; AGIRE ORA = X + Y &gt; Z. Livello di allerta (calcolato dal registro): Attivazione = almeno due fra AGIRE ORA, KRI in rosso, notizie in peggioramento; Attenzione = uno di questi, o margine sotto l'anno con P x I alto, presidio assente o KRI in ambra; Monitoraggio = gli altri. KRI = indicatore di rischio, di esposizione (quanto la Banca e' esposta) o di evoluzione (quanto cresce il fenomeno). ◆ = tema all'attenzione del supervisore.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="47">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="E41:H41"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A48:D48"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A45:D45"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="E39:H39"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A46:D46"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="A38:E38"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A40:E40"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="E3:F3"/>
-  </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CUso interno&amp;RHorizon Scan NFR</oddHeader>
-    <oddFooter>&amp;L&amp;F · &amp;A&amp;RPagina &amp;P di &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3907,7 +3305,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>10 · NFR-09 · Violazione di sanzioni internazionali tramite triangolazioni</t>
+          <t>9 · NFR-09 · Violazione di sanzioni internazionali tramite triangolazioni</t>
         </is>
       </c>
       <c r="B2" s="18" t="n"/>
@@ -3925,7 +3323,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>L1-04 · Clientela, prodotti e prassi professionali</t>
+          <t>9.4 · Legale</t>
         </is>
       </c>
       <c r="B3" s="21" t="n"/>
@@ -4051,7 +3449,7 @@
           <t>Probabilita</t>
         </is>
       </c>
-      <c r="B14" s="58" t="n">
+      <c r="B14" s="59" t="n">
         <v>2</v>
       </c>
       <c r="C14" s="29" t="inlineStr">
@@ -4071,7 +3469,7 @@
           <t>Prossimita</t>
         </is>
       </c>
-      <c r="B15" s="58" t="n">
+      <c r="B15" s="59" t="n">
         <v>2</v>
       </c>
       <c r="C15" s="29" t="inlineStr">
@@ -4127,7 +3525,7 @@
       <c r="H19" s="24" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>Livello di allerta: Monitoraggio — nessun segnale forte.</t>
         </is>
@@ -4216,10 +3614,10 @@
       <c r="B28" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="60" t="n">
+      <c r="C28" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="D28" s="60" t="n">
+      <c r="D28" s="57" t="n">
         <v>2</v>
       </c>
       <c r="E28" s="35" t="n">
@@ -4238,10 +3636,10 @@
       <c r="B29" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C29" s="60" t="n">
+      <c r="C29" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="D29" s="60" t="n">
+      <c r="D29" s="57" t="n">
         <v>2</v>
       </c>
       <c r="E29" s="35" t="n">
@@ -4260,10 +3658,10 @@
       <c r="B30" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C30" s="60" t="n">
+      <c r="C30" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="D30" s="60" t="n">
+      <c r="D30" s="57" t="n">
         <v>2</v>
       </c>
       <c r="E30" s="35" t="n">
@@ -4282,10 +3680,10 @@
       <c r="B31" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C31" s="60" t="n">
+      <c r="C31" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="60" t="n">
+      <c r="D31" s="57" t="n">
         <v>2</v>
       </c>
       <c r="E31" s="35" t="n">
@@ -4578,7 +3976,7 @@
       <c r="G62" s="52" t="n">
         <v>4.2</v>
       </c>
-      <c r="H62" s="57" t="inlineStr">
+      <c r="H62" s="58" t="inlineStr">
         <is>
           <t>Ambra</t>
         </is>
@@ -4619,7 +4017,7 @@
       <c r="G64" s="52" t="n">
         <v>9</v>
       </c>
-      <c r="H64" s="57" t="inlineStr">
+      <c r="H64" s="58" t="inlineStr">
         <is>
           <t>Ambra</t>
         </is>
@@ -4718,6 +4116,864 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Horizon Scan NFR — schede dei rischi · ciclo 2026Q4 · dati al 31/12/2026 · validato · Uso interno</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>10 · NFR-04 · Eventi climatici estremi su sedi e data center</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="19" t="inlineStr">
+        <is>
+          <t>score 2,80   ● 0,00   ·   Entro l'anno   ·   Attenzione</t>
+        </is>
+      </c>
+      <c r="H2" s="18" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>9.8 · Sicurezza fisica</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="n"/>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Driver: DRV-CLI</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Owner: Funzione Business Continuity · Presidio: Non verificato</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Esito: Confermato · validato</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>Il rischio</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
+      <c r="H5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Alluvioni o ondate di calore che rendono inagibili sedi operative o degradano il data center secondario.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Razionale: il fenomeno in termini di rischio</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="24" t="n"/>
+      <c r="G8" s="24" t="n"/>
+      <c r="H8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="46.5" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Eventi climatici estremi sempre piu' frequenti, alluvioni e ondate di calore (causa), possono rendere inagibili sedi operative o degradare il data center secondario (evento); le attivita' di quelle sedi si fermano e il ripristino costa, con disagi per i clienti (danno). Nessun evento sulle sedi nel trimestre e piani per le due sedi critiche in redazione: valori confermati.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>Valutazione, dimensione per dimensione (valori validati)</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>Dimensione</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Valore</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Perche' questo valore: informazioni e documenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Impatto</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Rilevante. La Mappa del rischio idrogeologico delle sedi (BCM) indica sedi critiche esposte, il cui blocco degrada processi critici.</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="33" customHeight="1">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Probabilita</t>
+        </is>
+      </c>
+      <c r="B14" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>Possibile. L'alluvione in Emilia-Romagna con chiusura di due filiali e' un caso in aziende comparabili e la Banca ha sedi nelle aree a rischio della Mappa.</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>Prossimita</t>
+        </is>
+      </c>
+      <c r="B15" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Da uno a due anni. Nessun evento in corso sulle sedi della Banca.</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="33" customHeight="1">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="B16" s="59" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>Da sei a dodici mesi. L'evento e' rapido, ma le attivita' si spostano sulle altre sedi e il danno pieno arriva solo se l'inagibilita' dura mesi (Mappa del rischio idrogeologico, BCM).</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Score composito 2,80 = (0,35 x 3 + 0,25 x 3 + 0,20 x 3 + 0,20 x 2) / 1,00. La rilevanza delle fonti e' nella tabella Fonti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>Urgenza (disuguaglianza di Mosca) e livello di allerta</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="24" t="n"/>
+      <c r="H19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="56" t="inlineStr">
+        <is>
+          <t>Livello di allerta: Attenzione — margine sotto l'anno con KRI in ambra o rosso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Agire entro l'anno. Tempo necessario X + Y = 0,25 + 0,50 = 0,75 anni; tempo disponibile Z = 1,5 anni (Prossimita 3). Margine Z - (X + Y) = 0,75.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>Cosa e' cambiato nel ciclo</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="24" t="n"/>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="24" t="n"/>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>Nessun valore cambiato: confermato sulle fonti del ciclo precedente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>Andamento negli ultimi trimestri</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>Ciclo</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>Imp</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>Prob</t>
+        </is>
+      </c>
+      <c r="D27" s="33" t="inlineStr">
+        <is>
+          <t>Pross</t>
+        </is>
+      </c>
+      <c r="E27" s="33" t="inlineStr">
+        <is>
+          <t>Vel</t>
+        </is>
+      </c>
+      <c r="F27" s="33" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="B28" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="37" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="B29" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="37" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="37" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="B31" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="37" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t>2026Q4</t>
+        </is>
+      </c>
+      <c r="B32" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="37" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>Fonti</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="n"/>
+      <c r="C47" s="24" t="n"/>
+      <c r="D47" s="24" t="n"/>
+      <c r="E47" s="24" t="n"/>
+      <c r="F47" s="24" t="n"/>
+      <c r="G47" s="24" t="n"/>
+      <c r="H47" s="24" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="F48" s="26" t="inlineStr">
+        <is>
+          <t>Rilevanza</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="n"/>
+    </row>
+    <row r="49" ht="18.5" customHeight="1">
+      <c r="A49" s="39" t="inlineStr">
+        <is>
+          <t>Mappa del rischio idrogeologico delle sedi — BCM</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="40" t="inlineStr">
+        <is>
+          <t>30/10/2025</t>
+        </is>
+      </c>
+      <c r="E49" s="41" t="inlineStr">
+        <is>
+          <t>Interna</t>
+        </is>
+      </c>
+      <c r="F49" s="42" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G49" s="39" t="n"/>
+      <c r="H49" s="6" t="n"/>
+    </row>
+    <row r="50" ht="18.5" customHeight="1">
+      <c r="A50" s="39" t="inlineStr">
+        <is>
+          <t>Alluvione in Emilia-Romagna con chiusura di due filiali</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="40" t="inlineStr">
+        <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="E50" s="43" t="inlineStr">
+        <is>
+          <t>Esterna</t>
+        </is>
+      </c>
+      <c r="F50" s="42" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G50" s="39" t="n"/>
+      <c r="H50" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>Azioni</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="n"/>
+      <c r="C52" s="24" t="n"/>
+      <c r="D52" s="24" t="n"/>
+      <c r="E52" s="24" t="n"/>
+      <c r="F52" s="24" t="n"/>
+      <c r="G52" s="24" t="n"/>
+      <c r="H52" s="24" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="26" t="inlineStr">
+        <is>
+          <t>Azione</t>
+        </is>
+      </c>
+      <c r="F53" s="26" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H53" s="26" t="inlineStr">
+        <is>
+          <t>Orizzonte · stato</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18.5" customHeight="1">
+      <c r="A54" s="45" t="inlineStr">
+        <is>
+          <t>• Redigere piani di continuita' specifici per le due sedi critiche in aree a rischio.</t>
+        </is>
+      </c>
+      <c r="F54" s="46" t="inlineStr">
+        <is>
+          <t>Funzione Business Continuity</t>
+        </is>
+      </c>
+      <c r="H54" s="46" t="inlineStr">
+        <is>
+          <t>12 mesi · Approvata (ciclo 2026Q2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="32" customHeight="1">
+      <c r="A55" s="47" t="inlineStr">
+        <is>
+          <t>Perche': Il KRI NFR-04-K1 mostra due sedi senza piano: e' il punto scoperto principale.</t>
+        </is>
+      </c>
+      <c r="B55" s="48" t="n"/>
+      <c r="C55" s="48" t="n"/>
+      <c r="D55" s="48" t="n"/>
+      <c r="E55" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: non indicato nel razionale di A1.</t>
+        </is>
+      </c>
+      <c r="F55" s="48" t="n"/>
+      <c r="G55" s="48" t="n"/>
+      <c r="H55" s="48" t="n"/>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="45" t="inlineStr">
+        <is>
+          <t>• Provare i piani di continuita' delle due sedi critiche con un'esercitazione di ripartenza in sede alternativa.</t>
+        </is>
+      </c>
+      <c r="F56" s="46" t="inlineStr">
+        <is>
+          <t>Funzione Business Continuity</t>
+        </is>
+      </c>
+      <c r="H56" s="46" t="inlineStr">
+        <is>
+          <t>6 mesi · Approvata (ciclo 2026Q3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="47" t="inlineStr">
+        <is>
+          <t>Perche': I piani delle due sedi (azione 2026Q2-NFR-04-A1) sono in redazione: senza una prova non si sa se reggono a un evento reale.</t>
+        </is>
+      </c>
+      <c r="B57" s="48" t="n"/>
+      <c r="C57" s="48" t="n"/>
+      <c r="D57" s="48" t="n"/>
+      <c r="E57" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: non indicato nel razionale di A1.</t>
+        </is>
+      </c>
+      <c r="F57" s="48" t="n"/>
+      <c r="G57" s="48" t="n"/>
+      <c r="H57" s="48" t="n"/>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="45" t="inlineStr">
+        <is>
+          <t>• Verificare con i fornitori di energia e telecomunicazioni delle due sedi critiche i tempi di ripristino garantiti dopo un'alluvione.</t>
+        </is>
+      </c>
+      <c r="F58" s="46" t="inlineStr">
+        <is>
+          <t>Funzione Business Continuity</t>
+        </is>
+      </c>
+      <c r="H58" s="46" t="inlineStr">
+        <is>
+          <t>6 mesi · Approvata (ciclo 2026Q4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="47" t="inlineStr">
+        <is>
+          <t>Perche': I piani delle due sedi (2026Q2-NFR-04-A1) e la loro prova (2026Q3-NFR-04-A1) presuppongono energia e rete disponibili, ma nessuno ha verificato in quanto tempo i fornitori le ripristinano.</t>
+        </is>
+      </c>
+      <c r="B59" s="48" t="n"/>
+      <c r="C59" s="48" t="n"/>
+      <c r="D59" s="48" t="n"/>
+      <c r="E59" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: Piani con tempi di ripartenza realistici; i giorni di indisponibilita' dopo un evento (NFR-04-K2) restano sotto la soglia di attenzione.</t>
+        </is>
+      </c>
+      <c r="F59" s="48" t="n"/>
+      <c r="G59" s="48" t="n"/>
+      <c r="H59" s="48" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>KRI in vigore</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="n"/>
+      <c r="C61" s="24" t="n"/>
+      <c r="D61" s="24" t="n"/>
+      <c r="E61" s="24" t="n"/>
+      <c r="F61" s="24" t="n"/>
+      <c r="G61" s="24" t="n"/>
+      <c r="H61" s="24" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="49" t="inlineStr">
+        <is>
+          <t>Indicatore</t>
+        </is>
+      </c>
+      <c r="E62" s="49" t="inlineStr">
+        <is>
+          <t>Valore</t>
+        </is>
+      </c>
+      <c r="F62" s="49" t="inlineStr">
+        <is>
+          <t>Soglie (attenzione / allerta)</t>
+        </is>
+      </c>
+      <c r="G62" s="49" t="inlineStr">
+        <is>
+          <t>Ciclo prima</t>
+        </is>
+      </c>
+      <c r="H62" s="49" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="50" t="inlineStr">
+        <is>
+          <t>[Esposizione] Sedi critiche in aree a rischio idrogeologico senza piano specifico (n)</t>
+        </is>
+      </c>
+      <c r="E63" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="52" t="inlineStr">
+        <is>
+          <t>1,0 / 3,0</t>
+        </is>
+      </c>
+      <c r="G63" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" s="58" t="inlineStr">
+        <is>
+          <t>Ambra</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="47" t="inlineStr">
+        <is>
+          <t>Perche' lo misuriamo: Misura l'esposizione: ogni sede critica senza piano specifico e' un punto in cui un'alluvione ferma l'operativita'.</t>
+        </is>
+      </c>
+      <c r="B64" s="48" t="n"/>
+      <c r="C64" s="48" t="n"/>
+      <c r="D64" s="48" t="n"/>
+      <c r="E64" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: Atteso a zero dopo i piani di continuita'; se torna a salire, nuove sedi sono entrate nelle aree a rischio della Mappa.</t>
+        </is>
+      </c>
+      <c r="F64" s="48" t="n"/>
+      <c r="G64" s="48" t="n"/>
+      <c r="H64" s="48" t="n"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="50" t="inlineStr">
+        <is>
+          <t>[Evoluzione] Giorni di indisponibilita' di sedi per eventi climatici (giorni)</t>
+        </is>
+      </c>
+      <c r="E65" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="52" t="inlineStr">
+        <is>
+          <t>2,0 / 5,0</t>
+        </is>
+      </c>
+      <c r="G65" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="54" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="47" t="inlineStr">
+        <is>
+          <t>Perche' lo misuriamo: Misura quanto il fenomeno colpisce davvero le sedi della Banca: i giorni persi per eventi climatici.</t>
+        </is>
+      </c>
+      <c r="B66" s="48" t="n"/>
+      <c r="C66" s="48" t="n"/>
+      <c r="D66" s="48" t="n"/>
+      <c r="E66" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: Pochi giorni e in calo con i piani di continuita'; oltre la soglia di allerta il rischio si sta manifestando e la Prossimita' va rivista.</t>
+        </is>
+      </c>
+      <c r="F66" s="48" t="n"/>
+      <c r="G66" s="48" t="n"/>
+      <c r="H66" s="48" t="n"/>
+    </row>
+    <row r="68" ht="61" customHeight="1">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>Legenda — Imp = Impatto, Prob = Probabilita, Pross = Prossimita, Vel = Velocity (1-5, 5 = peggiore; n.v. = non valutata, nessuna fonte ne documenta i tempi). Rilevanza di una fonte per la previsione: Alta = fonte primaria o caso documentato, Media = fonte specializzata, Bassa = generalista. Presidio = giudizio della Banca sui controlli, fuori dallo score. X = anni per decidere e avviare la mitigazione; Y = anni per mitigare (azioni o adeguamento strutturale); Z = anni prima che il rischio possa manifestarsi; AGIRE ORA = X + Y &gt; Z. Livello di allerta (calcolato dal registro): Attivazione = almeno due fra AGIRE ORA, KRI in rosso, notizie in peggioramento; Attenzione = uno di questi, o margine sotto l'anno con P x I alto, presidio assente o KRI in ambra; Monitoraggio = gli altri. KRI = indicatore di rischio, di esposizione (quanto la Banca e' esposta) o di evoluzione (quanto cresce il fenomeno). ◆ = tema all'attenzione del supervisore.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="51">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;CUso interno&amp;RHorizon Scan NFR</oddHeader>
+    <oddFooter>&amp;L&amp;F · &amp;A&amp;RPagina &amp;P di &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4747,7 +5003,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>11 · NFR-04 · Eventi climatici estremi su sedi e data center</t>
+          <t>11 · NFR-11 · Fine del supporto dei sistemi di pagamento legacy</t>
         </is>
       </c>
       <c r="B2" s="18" t="n"/>
@@ -4757,7 +5013,7 @@
       <c r="F2" s="18" t="n"/>
       <c r="G2" s="19" t="inlineStr">
         <is>
-          <t>score 2,80   ● 0,00   ·   Entro l'anno   ·   Attenzione</t>
+          <t>score 2,80   ● 0,00   ·   AGIRE ORA   ·   Attivazione</t>
         </is>
       </c>
       <c r="H2" s="18" t="n"/>
@@ -4765,19 +5021,19 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>L1-05 · Danni a beni materiali</t>
+          <t>9.6 · Tecnologico</t>
         </is>
       </c>
       <c r="B3" s="21" t="n"/>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>Driver: DRV-CLI</t>
+          <t>Driver: DRV-TEC</t>
         </is>
       </c>
       <c r="D3" s="21" t="n"/>
       <c r="E3" s="20" t="inlineStr">
         <is>
-          <t>Owner: Funzione Business Continuity · Presidio: Non verificato</t>
+          <t>Owner: Funzione IT Operations · Presidio: Assente</t>
         </is>
       </c>
       <c r="F3" s="21" t="n"/>
@@ -4805,7 +5061,7 @@
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>Alluvioni o ondate di calore che rendono inagibili sedi operative o degradano il data center secondario.</t>
+          <t>Componenti del sistema di pagamento fuori supporto del produttore, senza patch di sicurezza e con competenze interne in riduzione.</t>
         </is>
       </c>
     </row>
@@ -4823,10 +5079,10 @@
       <c r="G8" s="24" t="n"/>
       <c r="H8" s="24" t="n"/>
     </row>
-    <row r="9" ht="46.5" customHeight="1">
+    <row r="9" ht="33" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>Eventi climatici estremi sempre piu' frequenti, alluvioni e ondate di calore (causa), possono rendere inagibili sedi operative o degradare il data center secondario (evento); le attivita' di quelle sedi si fermano e il ripristino costa, con disagi per i clienti (danno). Nessun evento sulle sedi nel trimestre e piani per le due sedi critiche in redazione: valori confermati.</t>
+          <t>Componenti del sistema di pagamento non sono piu' supportate dal produttore e le competenze interne diminuiscono (causa); una vulnerabilita' senza patch viene sfruttata o un guasto non si sa piu' riparare (evento); i pagamenti si degradano o si fermano, con danno ai clienti (danno). Nessuna evidenza nuova nel trimestre: valori confermati.</t>
         </is>
       </c>
     </row>
@@ -4872,7 +5128,7 @@
       </c>
       <c r="C13" s="29" t="inlineStr">
         <is>
-          <t>Rilevante. La Mappa del rischio idrogeologico delle sedi (BCM) indica sedi critiche esposte, il cui blocco degrada processi critici.</t>
+          <t>Rilevante. L'Inventario delle componenti fuori supporto (IT) riguarda il sistema di pagamento, processo critico per molti clienti.</t>
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
@@ -4881,7 +5137,7 @@
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="6" t="n"/>
     </row>
-    <row r="14" ht="33" customHeight="1">
+    <row r="14" ht="26" customHeight="1">
       <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Probabilita</t>
@@ -4892,7 +5148,7 @@
       </c>
       <c r="C14" s="29" t="inlineStr">
         <is>
-          <t>Possibile. L'alluvione in Emilia-Romagna con chiusura di due filiali e' un caso in aziende comparabili e la Banca ha sedi nelle aree a rischio della Mappa.</t>
+          <t>Possibile. La Comunicazione del produttore sulla fine del supporto esteso conferma che non arriveranno piu' patch: la Banca e' esposta.</t>
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
@@ -4912,7 +5168,7 @@
       </c>
       <c r="C15" s="29" t="inlineStr">
         <is>
-          <t>Da uno a due anni. Nessun evento in corso sulle sedi della Banca.</t>
+          <t>Da uno a due anni. Nessun incidente in corso; il rischio cresce con il tempo senza patch.</t>
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
@@ -4921,18 +5177,18 @@
       <c r="G15" s="6" t="n"/>
       <c r="H15" s="6" t="n"/>
     </row>
-    <row r="16" ht="33" customHeight="1">
+    <row r="16" ht="26" customHeight="1">
       <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Velocity</t>
         </is>
       </c>
-      <c r="B16" s="58" t="n">
+      <c r="B16" s="59" t="n">
         <v>2</v>
       </c>
       <c r="C16" s="29" t="inlineStr">
         <is>
-          <t>Da sei a dodici mesi. L'evento e' rapido, ma le attivita' si spostano sulle altre sedi e il danno pieno arriva solo se l'inagibilita' dura mesi (Mappa del rischio idrogeologico, BCM).</t>
+          <t>Da sei a dodici mesi. Le vulnerabilita' si accumulano gradualmente sulle componenti senza supporto (Inventario IT).</t>
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
@@ -4963,16 +5219,16 @@
       <c r="H19" s="24" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="56" t="inlineStr">
-        <is>
-          <t>Livello di allerta: Attenzione — margine sotto l'anno con KRI in ambra o rosso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>Agire entro l'anno. Tempo necessario X + Y = 0,25 + 0,50 = 0,75 anni; tempo disponibile Z = 1,5 anni (Prossimita 3). Margine Z - (X + Y) = 0,75.</t>
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>Livello di allerta: Attivazione — AGIRE ORA; KRI in rosso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33" customHeight="1">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>AGIRE ORA: X+Y &gt; Z. Tempo necessario X + Y = 0,25 + 3,00 (con 3,0 anni di adeguamento strutturale, stimati da A1 e validati; motivo: stima; la sostituzione delle componenti legacy e' un programma pluriennale, che va oltre le azioni del ciclo) = 3,25 anni; tempo disponibile Z = 1,5 anni (Prossimita 3). Margine Z - (X + Y) = -1,75.</t>
         </is>
       </c>
     </row>
@@ -5055,14 +5311,14 @@
       <c r="C28" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="D28" s="60" t="n">
+      <c r="D28" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="60" t="n">
-        <v>2</v>
-      </c>
       <c r="F28" s="37" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="29">
@@ -5077,14 +5333,14 @@
       <c r="C29" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="D29" s="60" t="n">
+      <c r="D29" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="60" t="n">
-        <v>2</v>
-      </c>
       <c r="F29" s="37" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="30">
@@ -5102,7 +5358,7 @@
       <c r="D30" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="60" t="n">
+      <c r="E30" s="57" t="n">
         <v>2</v>
       </c>
       <c r="F30" s="37" t="n">
@@ -5124,7 +5380,7 @@
       <c r="D31" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="60" t="n">
+      <c r="E31" s="57" t="n">
         <v>2</v>
       </c>
       <c r="F31" s="37" t="n">
@@ -5146,7 +5402,7 @@
       <c r="D32" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="E32" s="60" t="n">
+      <c r="E32" s="57" t="n">
         <v>2</v>
       </c>
       <c r="F32" s="37" t="n">
@@ -5193,14 +5449,14 @@
     <row r="49" ht="18.5" customHeight="1">
       <c r="A49" s="39" t="inlineStr">
         <is>
-          <t>Mappa del rischio idrogeologico delle sedi — BCM</t>
+          <t>Inventario delle componenti fuori supporto — IT</t>
         </is>
       </c>
       <c r="B49" s="6" t="n"/>
       <c r="C49" s="6" t="n"/>
       <c r="D49" s="40" t="inlineStr">
         <is>
-          <t>30/10/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="E49" s="41" t="inlineStr">
@@ -5216,17 +5472,17 @@
       <c r="G49" s="39" t="n"/>
       <c r="H49" s="6" t="n"/>
     </row>
-    <row r="50" ht="18.5" customHeight="1">
+    <row r="50" ht="32" customHeight="1">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>Alluvione in Emilia-Romagna con chiusura di due filiali</t>
+          <t>Comunicazione del produttore sulla fine del supporto esteso</t>
         </is>
       </c>
       <c r="B50" s="6" t="n"/>
       <c r="C50" s="6" t="n"/>
       <c r="D50" s="40" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>31/01/2026</t>
         </is>
       </c>
       <c r="E50" s="43" t="inlineStr">
@@ -5234,9 +5490,9 @@
           <t>Esterna</t>
         </is>
       </c>
-      <c r="F50" s="42" t="inlineStr">
-        <is>
-          <t>Alta</t>
+      <c r="F50" s="44" t="inlineStr">
+        <is>
+          <t>Media</t>
         </is>
       </c>
       <c r="G50" s="39" t="n"/>
@@ -5276,12 +5532,12 @@
     <row r="54" ht="18.5" customHeight="1">
       <c r="A54" s="45" t="inlineStr">
         <is>
-          <t>• Redigere piani di continuita' specifici per le due sedi critiche in aree a rischio.</t>
+          <t>• Piano di sostituzione delle componenti fuori supporto del sistema di pagamento.</t>
         </is>
       </c>
       <c r="F54" s="46" t="inlineStr">
         <is>
-          <t>Funzione Business Continuity</t>
+          <t>Funzione IT Operations</t>
         </is>
       </c>
       <c r="H54" s="46" t="inlineStr">
@@ -5290,10 +5546,10 @@
         </is>
       </c>
     </row>
-    <row r="55" ht="32" customHeight="1">
+    <row r="55" ht="19" customHeight="1">
       <c r="A55" s="47" t="inlineStr">
         <is>
-          <t>Perche': Il KRI NFR-04-K1 mostra due sedi senza piano: e' il punto scoperto principale.</t>
+          <t>Perche': Oggi non ci sono patch per le componenti fuori supporto.</t>
         </is>
       </c>
       <c r="B55" s="48" t="n"/>
@@ -5311,24 +5567,24 @@
     <row r="56" ht="32" customHeight="1">
       <c r="A56" s="45" t="inlineStr">
         <is>
-          <t>• Provare i piani di continuita' delle due sedi critiche con un'esercitazione di ripartenza in sede alternativa.</t>
+          <t>• Isolare in un segmento di rete dedicato le componenti fuori supporto del sistema di pagamento, in attesa della sostituzione.</t>
         </is>
       </c>
       <c r="F56" s="46" t="inlineStr">
         <is>
-          <t>Funzione Business Continuity</t>
+          <t>Funzione IT Operations</t>
         </is>
       </c>
       <c r="H56" s="46" t="inlineStr">
         <is>
-          <t>6 mesi · Approvata (ciclo 2026Q3)</t>
+          <t>12 mesi · Approvata (ciclo 2026Q3)</t>
         </is>
       </c>
     </row>
     <row r="57" ht="32" customHeight="1">
       <c r="A57" s="47" t="inlineStr">
         <is>
-          <t>Perche': I piani delle due sedi (azione 2026Q2-NFR-04-A1) sono in redazione: senza una prova non si sa se reggono a un evento reale.</t>
+          <t>Perche': La sostituzione (2026Q2-NFR-11-A1) richiede anni: l'isolamento riduce subito la superficie di attacco.</t>
         </is>
       </c>
       <c r="B57" s="48" t="n"/>
@@ -5346,24 +5602,24 @@
     <row r="58" ht="32" customHeight="1">
       <c r="A58" s="45" t="inlineStr">
         <is>
-          <t>• Verificare con i fornitori di energia e telecomunicazioni delle due sedi critiche i tempi di ripristino garantiti dopo un'alluvione.</t>
+          <t>• Ottenere dal produttore un supporto esteso a pagamento per le componenti fuori supporto piu' critiche, fino alla sostituzione.</t>
         </is>
       </c>
       <c r="F58" s="46" t="inlineStr">
         <is>
-          <t>Funzione Business Continuity</t>
+          <t>Funzione IT Operations</t>
         </is>
       </c>
       <c r="H58" s="46" t="inlineStr">
         <is>
-          <t>6 mesi · Approvata (ciclo 2026Q4)</t>
+          <t>12 mesi · Approvata (ciclo 2026Q4)</t>
         </is>
       </c>
     </row>
     <row r="59" ht="45" customHeight="1">
       <c r="A59" s="47" t="inlineStr">
         <is>
-          <t>Perche': I piani delle due sedi (2026Q2-NFR-04-A1) e la loro prova (2026Q3-NFR-04-A1) presuppongono energia e rete disponibili, ma nessuno ha verificato in quanto tempo i fornitori le ripristinano.</t>
+          <t>Perche': La sostituzione (2026Q2-NFR-11-A1) e' un programma pluriennale e l'isolamento (2026Q3-NFR-11-A1) non corregge le vulnerabilita': il supporto esteso riporta le patch sulle componenti piu' esposte.</t>
         </is>
       </c>
       <c r="B59" s="48" t="n"/>
@@ -5371,7 +5627,7 @@
       <c r="D59" s="48" t="n"/>
       <c r="E59" s="47" t="inlineStr">
         <is>
-          <t>Effetto atteso: Piani con tempi di ripartenza realistici; i giorni di indisponibilita' dopo un evento (NFR-04-K2) restano sotto la soglia di attenzione.</t>
+          <t>Effetto atteso: Il numero di componenti senza patch (NFR-11-K1) inizia a scendere; il rischio resta urgente finche' il programma non e' avanzato.</t>
         </is>
       </c>
       <c r="F59" s="48" t="n"/>
@@ -5422,21 +5678,21 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="50" t="inlineStr">
         <is>
-          <t>[Esposizione] Sedi critiche in aree a rischio idrogeologico senza piano specifico (n)</t>
+          <t>[Esposizione] Componenti del sistema di pagamento fuori supporto (n)</t>
         </is>
       </c>
       <c r="E63" s="51" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F63" s="52" t="inlineStr">
         <is>
-          <t>1,0 / 3,0</t>
+          <t>3,0 / 8,0</t>
         </is>
       </c>
       <c r="G63" s="52" t="n">
-        <v>2</v>
-      </c>
-      <c r="H63" s="57" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="H63" s="58" t="inlineStr">
         <is>
           <t>Ambra</t>
         </is>
@@ -5445,7 +5701,7 @@
     <row r="64" ht="32" customHeight="1">
       <c r="A64" s="47" t="inlineStr">
         <is>
-          <t>Perche' lo misuriamo: Misura l'esposizione: ogni sede critica senza piano specifico e' un punto in cui un'alluvione ferma l'operativita'.</t>
+          <t>Perche' lo misuriamo: Misura quanta parte del sistema di pagamento e' senza supporto: e' l'esposizione della Banca.</t>
         </is>
       </c>
       <c r="B64" s="48" t="n"/>
@@ -5453,7 +5709,7 @@
       <c r="D64" s="48" t="n"/>
       <c r="E64" s="47" t="inlineStr">
         <is>
-          <t>Effetto atteso: Atteso a zero dopo i piani di continuita'; se torna a salire, nuove sedi sono entrate nelle aree a rischio della Mappa.</t>
+          <t>Effetto atteso: In calo con il piano di sostituzione; se sale, altre componenti sono uscite dal supporto.</t>
         </is>
       </c>
       <c r="F64" s="48" t="n"/>
@@ -5463,30 +5719,30 @@
     <row r="65" ht="20" customHeight="1">
       <c r="A65" s="50" t="inlineStr">
         <is>
-          <t>[Evoluzione] Giorni di indisponibilita' di sedi per eventi climatici (giorni)</t>
+          <t>[Evoluzione] Vulnerabilita' senza patch disponibile sui sistemi legacy (n)</t>
         </is>
       </c>
       <c r="E65" s="51" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F65" s="52" t="inlineStr">
         <is>
-          <t>2,0 / 5,0</t>
+          <t>2,0 / 6,0</t>
         </is>
       </c>
       <c r="G65" s="52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="54" t="inlineStr">
-        <is>
-          <t>Verde</t>
+        <v>5</v>
+      </c>
+      <c r="H65" s="53" t="inlineStr">
+        <is>
+          <t>Rosso</t>
         </is>
       </c>
     </row>
     <row r="66" ht="32" customHeight="1">
       <c r="A66" s="47" t="inlineStr">
         <is>
-          <t>Perche' lo misuriamo: Misura quanto il fenomeno colpisce davvero le sedi della Banca: i giorni persi per eventi climatici.</t>
+          <t>Perche' lo misuriamo: Misura quanto cresce la minaccia sulle componenti senza supporto.</t>
         </is>
       </c>
       <c r="B66" s="48" t="n"/>
@@ -5494,7 +5750,7 @@
       <c r="D66" s="48" t="n"/>
       <c r="E66" s="47" t="inlineStr">
         <is>
-          <t>Effetto atteso: Pochi giorni e in calo con i piani di continuita'; oltre la soglia di allerta il rischio si sta manifestando e la Prossimita' va rivista.</t>
+          <t>Effetto atteso: Cresce nel tempo finche' le componenti restano; oltre la soglia di allerta servono subito misure compensative.</t>
         </is>
       </c>
       <c r="F66" s="48" t="n"/>
@@ -5582,7 +5838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5605,7 +5861,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>12 · NFR-11 · Fine del supporto dei sistemi di pagamento legacy</t>
+          <t>12 · NFR-16 · Vertenze e carenza di tecnici nei ruoli IT critici</t>
         </is>
       </c>
       <c r="B2" s="18" t="n"/>
@@ -5615,7 +5871,7 @@
       <c r="F2" s="18" t="n"/>
       <c r="G2" s="19" t="inlineStr">
         <is>
-          <t>score 2,80   ● 0,00   ·   AGIRE ORA   ·   Attivazione</t>
+          <t>score 2,80   ▲ +0,61   ·   Margine 1,8 anni   ·   Monitoraggio</t>
         </is>
       </c>
       <c r="H2" s="18" t="n"/>
@@ -5623,26 +5879,26 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>L1-06 · Interruzione dell'operativita' e disfunzione dei sistemi</t>
+          <t>9.11 · Employer</t>
         </is>
       </c>
       <c r="B3" s="21" t="n"/>
       <c r="C3" s="20" t="inlineStr">
         <is>
-          <t>Driver: DRV-TEC</t>
+          <t>Driver: DRV-HUM, DRV-TEC</t>
         </is>
       </c>
       <c r="D3" s="21" t="n"/>
       <c r="E3" s="20" t="inlineStr">
         <is>
-          <t>Owner: Funzione IT Operations · Presidio: Assente</t>
+          <t>Owner: Da assegnare · Presidio: Non verificato</t>
         </is>
       </c>
       <c r="F3" s="21" t="n"/>
       <c r="G3" s="20" t="n"/>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>Esito: Confermato · validato</t>
+          <t>Esito: Variato · validato</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5919,7 @@
     <row r="6" ht="19.5" customHeight="1">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>Componenti del sistema di pagamento fuori supporto del produttore, senza patch di sicurezza e con competenze interne in riduzione.</t>
+          <t>Scioperi di settore e uscite di personale tecnico non rimpiazzabile che lasciano scoperti ruoli IT critici, con violazioni di obblighi di lavoro e sicurezza nei turni di copertura.</t>
         </is>
       </c>
     </row>
@@ -5681,10 +5937,10 @@
       <c r="G8" s="24" t="n"/>
       <c r="H8" s="24" t="n"/>
     </row>
-    <row r="9" ht="33" customHeight="1">
+    <row r="9" ht="46.5" customHeight="1">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>Componenti del sistema di pagamento non sono piu' supportate dal produttore e le competenze interne diminuiscono (causa); una vulnerabilita' senza patch viene sfruttata o un guasto non si sa piu' riparare (evento); i pagamenti si degradano o si fermano, con danno ai clienti (danno). Nessuna evidenza nuova nel trimestre: valori confermati.</t>
+          <t>La vertenza nazionale del settore e le uscite di tecnici difficili da sostituire (causa) lasciano scoperti ruoli IT critici durante scioperi o dimissioni, con turni di copertura che violano obblighi di lavoro e sicurezza (evento); processi critici si degradano e la Banca rischia vertenze e sanzioni (danno). Era in osservazione dal 2026Q3: il segnale di avvicinamento si e' verificato e il rischio entra nel radar.</t>
         </is>
       </c>
     </row>
@@ -5719,7 +5975,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="26" customHeight="1">
+    <row r="13" ht="33" customHeight="1">
       <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Impatto</t>
@@ -5730,7 +5986,7 @@
       </c>
       <c r="C13" s="29" t="inlineStr">
         <is>
-          <t>Rilevante. L'Inventario delle componenti fuori supporto (IT) riguarda il sistema di pagamento, processo critico per molti clienti.</t>
+          <t>Rilevante. Durante le astensioni si degradano processi critici che dipendono da pochi tecnici (Piano di successione dei ruoli IT critici, Direzione Risorse Umane).</t>
         </is>
       </c>
       <c r="D13" s="6" t="n"/>
@@ -5739,7 +5995,7 @@
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="6" t="n"/>
     </row>
-    <row r="14" ht="26" customHeight="1">
+    <row r="14" ht="33" customHeight="1">
       <c r="A14" s="27" t="inlineStr">
         <is>
           <t>Probabilita</t>
@@ -5750,7 +6006,7 @@
       </c>
       <c r="C14" s="29" t="inlineStr">
         <is>
-          <t>Possibile. La Comunicazione del produttore sulla fine del supporto esteso conferma che non arriveranno piu' patch: la Banca e' esposta.</t>
+          <t>Possibile. Lo sciopero nazionale del personale bancario e la carenza di tecnici IT sono in corso nel settore; la Banca e' esposta perche' il Piano di successione copre solo una parte dei ruoli.</t>
         </is>
       </c>
       <c r="D14" s="6" t="n"/>
@@ -5765,12 +6021,12 @@
           <t>Prossimita</t>
         </is>
       </c>
-      <c r="B15" s="55" t="n">
-        <v>3</v>
+      <c r="B15" s="59" t="n">
+        <v>2</v>
       </c>
       <c r="C15" s="29" t="inlineStr">
         <is>
-          <t>Da uno a due anni. Nessun incidente in corso; il rischio cresce con il tempo senza patch.</t>
+          <t>Da due a tre anni. La vertenza e' in corso nel settore, senza astensioni annunciate presso la Banca.</t>
         </is>
       </c>
       <c r="D15" s="6" t="n"/>
@@ -5785,12 +6041,12 @@
           <t>Velocity</t>
         </is>
       </c>
-      <c r="B16" s="58" t="n">
-        <v>2</v>
+      <c r="B16" s="55" t="n">
+        <v>3</v>
       </c>
       <c r="C16" s="29" t="inlineStr">
         <is>
-          <t>Da sei a dodici mesi. Le vulnerabilita' si accumulano gradualmente sulle componenti senza supporto (Inventario IT).</t>
+          <t>Da tre a sei mesi. Le uscite di personale e i periodi di vertenza si sviluppano in alcuni mesi (Sciopero nazionale del personale bancario).</t>
         </is>
       </c>
       <c r="D16" s="6" t="n"/>
@@ -5802,7 +6058,7 @@
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Score composito 2,80 = (0,35 x 3 + 0,25 x 3 + 0,20 x 3 + 0,20 x 2) / 1,00. La rilevanza delle fonti e' nella tabella Fonti.</t>
+          <t>Score composito 2,80 = (0,35 x 3 + 0,25 x 3 + 0,20 x 2 + 0,20 x 3) / 1,00. La rilevanza delle fonti e' nella tabella Fonti.</t>
         </is>
       </c>
     </row>
@@ -5821,16 +6077,16 @@
       <c r="H19" s="24" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="32" t="inlineStr">
-        <is>
-          <t>Livello di allerta: Attivazione — AGIRE ORA; KRI in rosso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="33" customHeight="1">
-      <c r="A21" s="32" t="inlineStr">
-        <is>
-          <t>AGIRE ORA: X+Y &gt; Z. Tempo necessario X + Y = 0,25 + 3,00 (con 3,0 anni di adeguamento strutturale, stimati da A1 e validati; motivo: stima; la sostituzione delle componenti legacy e' un programma pluriennale, che va oltre le azioni del ciclo) = 3,25 anni; tempo disponibile Z = 1,5 anni (Prossimita 3). Margine Z - (X + Y) = -1,75.</t>
+      <c r="A20" s="60" t="inlineStr">
+        <is>
+          <t>Livello di allerta: Monitoraggio — nessun segnale forte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Margine 1,8 anni. Tempo necessario X + Y = 0,25 + 0,50 = 0,75 anni; tempo disponibile Z = 2,5 anni (Prossimita 2). Margine Z - (X + Y) = 1,75.</t>
         </is>
       </c>
     </row>
@@ -5848,10 +6104,12 @@
       <c r="G23" s="24" t="n"/>
       <c r="H23" s="24" t="n"/>
     </row>
-    <row r="24" ht="19.5" customHeight="1">
+    <row r="24" ht="87" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>Nessun valore cambiato: confermato sulle fonti del ciclo precedente.</t>
+          <t>• Probabilita 2 → 3: Lo sciopero nazionale del personale bancario di ottobre ha coinvolto i tecnici IT e il piano di successione della Banca copre solo meta' dei ruoli critici: la Banca e' esposta. (15/11/2026)
+• Prossimita 1 → 2: La vertenza nazionale e' in corso nel settore dal 6 ottobre 2026, con due giornate di sciopero proclamate: il fenomeno puo' toccare la Banca entro tre anni. (06/10/2026)
+• Velocity n.v. → 3: Lo sciopero nazionale del personale bancario documenta che uscite di personale e periodi di vertenza si sviluppano in alcuni mesi: velocity valutata per la prima volta. (06/10/2026)</t>
         </is>
       </c>
     </row>
@@ -5904,29 +6162,31 @@
     <row r="28">
       <c r="A28" s="34" t="inlineStr">
         <is>
-          <t>2025Q4</t>
+          <t>2026Q3</t>
         </is>
       </c>
       <c r="B28" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="60" t="n">
+      <c r="C28" s="57" t="n">
         <v>2</v>
       </c>
+      <c r="D28" s="62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="61" t="inlineStr">
+        <is>
+          <t>n.v.</t>
+        </is>
+      </c>
       <c r="F28" s="37" t="n">
-        <v>2.8</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="34" t="inlineStr">
         <is>
-          <t>2026Q1</t>
+          <t>2026Q4</t>
         </is>
       </c>
       <c r="B29" s="35" t="n">
@@ -5935,293 +6195,278 @@
       <c r="C29" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="D29" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" s="60" t="n">
+      <c r="D29" s="57" t="n">
         <v>2</v>
+      </c>
+      <c r="E29" s="35" t="n">
+        <v>3</v>
       </c>
       <c r="F29" s="37" t="n">
         <v>2.8</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="34" t="inlineStr">
-        <is>
-          <t>2026Q2</t>
-        </is>
-      </c>
-      <c r="B30" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C30" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D30" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" s="60" t="n">
-        <v>2</v>
-      </c>
-      <c r="F30" s="37" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="34" t="inlineStr">
-        <is>
-          <t>2026Q3</t>
-        </is>
-      </c>
-      <c r="B31" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C31" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D31" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="60" t="n">
-        <v>2</v>
-      </c>
-      <c r="F31" s="37" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="34" t="inlineStr">
-        <is>
-          <t>2026Q4</t>
-        </is>
-      </c>
-      <c r="B32" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" s="60" t="n">
-        <v>2</v>
-      </c>
-      <c r="F32" s="37" t="n">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="23" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="23" t="inlineStr">
         <is>
           <t>Fonti</t>
         </is>
       </c>
-      <c r="B47" s="24" t="n"/>
-      <c r="C47" s="24" t="n"/>
-      <c r="D47" s="24" t="n"/>
-      <c r="E47" s="24" t="n"/>
-      <c r="F47" s="24" t="n"/>
-      <c r="G47" s="24" t="n"/>
-      <c r="H47" s="24" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="26" t="inlineStr">
+      <c r="B44" s="24" t="n"/>
+      <c r="C44" s="24" t="n"/>
+      <c r="D44" s="24" t="n"/>
+      <c r="E44" s="24" t="n"/>
+      <c r="F44" s="24" t="n"/>
+      <c r="G44" s="24" t="n"/>
+      <c r="H44" s="24" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>Fonte</t>
         </is>
       </c>
-      <c r="D48" s="26" t="inlineStr">
+      <c r="D45" s="26" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
-      <c r="E48" s="26" t="inlineStr">
+      <c r="E45" s="26" t="inlineStr">
         <is>
           <t>Tipo</t>
         </is>
       </c>
-      <c r="F48" s="26" t="inlineStr">
+      <c r="F45" s="26" t="inlineStr">
         <is>
           <t>Rilevanza</t>
         </is>
       </c>
-      <c r="G48" s="26" t="n"/>
-    </row>
-    <row r="49" ht="18.5" customHeight="1">
-      <c r="A49" s="39" t="inlineStr">
-        <is>
-          <t>Inventario delle componenti fuori supporto — IT</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="40" t="inlineStr">
-        <is>
-          <t>30/09/2025</t>
-        </is>
-      </c>
-      <c r="E49" s="41" t="inlineStr">
+      <c r="G45" s="26" t="n"/>
+    </row>
+    <row r="46" ht="32" customHeight="1">
+      <c r="A46" s="39" t="inlineStr">
+        <is>
+          <t>Sciopero nazionale del personale bancario e carenza di tecnici IT</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="40" t="inlineStr">
+        <is>
+          <t>06/10/2026</t>
+        </is>
+      </c>
+      <c r="E46" s="43" t="inlineStr">
+        <is>
+          <t>Esterna</t>
+        </is>
+      </c>
+      <c r="F46" s="44" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="G46" s="39" t="n"/>
+      <c r="H46" s="6" t="n"/>
+    </row>
+    <row r="47" ht="32" customHeight="1">
+      <c r="A47" s="39" t="inlineStr">
+        <is>
+          <t>Piano di successione dei ruoli IT critici — Direzione Risorse Umane</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="40" t="inlineStr">
+        <is>
+          <t>15/11/2026</t>
+        </is>
+      </c>
+      <c r="E47" s="41" t="inlineStr">
         <is>
           <t>Interna</t>
         </is>
       </c>
-      <c r="F49" s="42" t="inlineStr">
+      <c r="F47" s="42" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="G49" s="39" t="n"/>
-      <c r="H49" s="6" t="n"/>
-    </row>
-    <row r="50" ht="32" customHeight="1">
-      <c r="A50" s="39" t="inlineStr">
-        <is>
-          <t>Comunicazione del produttore sulla fine del supporto esteso</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="40" t="inlineStr">
-        <is>
-          <t>31/01/2026</t>
-        </is>
-      </c>
-      <c r="E50" s="43" t="inlineStr">
-        <is>
-          <t>Esterna</t>
-        </is>
-      </c>
-      <c r="F50" s="44" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="G50" s="39" t="n"/>
-      <c r="H50" s="6" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="23" t="inlineStr">
+      <c r="G47" s="39" t="n"/>
+      <c r="H47" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="inlineStr">
         <is>
           <t>Azioni</t>
         </is>
       </c>
-      <c r="B52" s="24" t="n"/>
-      <c r="C52" s="24" t="n"/>
-      <c r="D52" s="24" t="n"/>
-      <c r="E52" s="24" t="n"/>
-      <c r="F52" s="24" t="n"/>
-      <c r="G52" s="24" t="n"/>
-      <c r="H52" s="24" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="26" t="inlineStr">
+      <c r="B49" s="24" t="n"/>
+      <c r="C49" s="24" t="n"/>
+      <c r="D49" s="24" t="n"/>
+      <c r="E49" s="24" t="n"/>
+      <c r="F49" s="24" t="n"/>
+      <c r="G49" s="24" t="n"/>
+      <c r="H49" s="24" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="26" t="inlineStr">
         <is>
           <t>Azione</t>
         </is>
       </c>
-      <c r="F53" s="26" t="inlineStr">
+      <c r="F50" s="26" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H53" s="26" t="inlineStr">
+      <c r="H50" s="26" t="inlineStr">
         <is>
           <t>Orizzonte · stato</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="18.5" customHeight="1">
-      <c r="A54" s="45" t="inlineStr">
-        <is>
-          <t>• Piano di sostituzione delle componenti fuori supporto del sistema di pagamento.</t>
-        </is>
-      </c>
-      <c r="F54" s="46" t="inlineStr">
-        <is>
-          <t>Funzione IT Operations</t>
-        </is>
-      </c>
-      <c r="H54" s="46" t="inlineStr">
-        <is>
-          <t>12 mesi · Approvata (ciclo 2026Q2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="A55" s="47" t="inlineStr">
-        <is>
-          <t>Perche': Oggi non ci sono patch per le componenti fuori supporto.</t>
-        </is>
-      </c>
-      <c r="B55" s="48" t="n"/>
-      <c r="C55" s="48" t="n"/>
-      <c r="D55" s="48" t="n"/>
-      <c r="E55" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: non indicato nel razionale di A1.</t>
-        </is>
-      </c>
-      <c r="F55" s="48" t="n"/>
-      <c r="G55" s="48" t="n"/>
-      <c r="H55" s="48" t="n"/>
-    </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="45" t="inlineStr">
-        <is>
-          <t>• Isolare in un segmento di rete dedicato le componenti fuori supporto del sistema di pagamento, in attesa della sostituzione.</t>
-        </is>
-      </c>
-      <c r="F56" s="46" t="inlineStr">
-        <is>
-          <t>Funzione IT Operations</t>
-        </is>
-      </c>
-      <c r="H56" s="46" t="inlineStr">
-        <is>
-          <t>12 mesi · Approvata (ciclo 2026Q3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="47" t="inlineStr">
-        <is>
-          <t>Perche': La sostituzione (2026Q2-NFR-11-A1) richiede anni: l'isolamento riduce subito la superficie di attacco.</t>
-        </is>
-      </c>
-      <c r="B57" s="48" t="n"/>
-      <c r="C57" s="48" t="n"/>
-      <c r="D57" s="48" t="n"/>
-      <c r="E57" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: non indicato nel razionale di A1.</t>
-        </is>
-      </c>
-      <c r="F57" s="48" t="n"/>
-      <c r="G57" s="48" t="n"/>
-      <c r="H57" s="48" t="n"/>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="45" t="inlineStr">
-        <is>
-          <t>• Ottenere dal produttore un supporto esteso a pagamento per le componenti fuori supporto piu' critiche, fino alla sostituzione.</t>
-        </is>
-      </c>
-      <c r="F58" s="46" t="inlineStr">
-        <is>
-          <t>Funzione IT Operations</t>
-        </is>
-      </c>
-      <c r="H58" s="46" t="inlineStr">
-        <is>
-          <t>12 mesi · Approvata (ciclo 2026Q4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
+    <row r="51" ht="18.5" customHeight="1">
+      <c r="A51" s="45" t="inlineStr">
+        <is>
+          <t>• Estendere il piano di successione a tutti i ruoli IT critici, con backup formati.</t>
+        </is>
+      </c>
+      <c r="F51" s="46" t="inlineStr">
+        <is>
+          <t>Direzione Risorse Umane</t>
+        </is>
+      </c>
+      <c r="H51" s="46" t="inlineStr">
+        <is>
+          <t>6 mesi · Approvata (ciclo 2026Q4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="47" t="inlineStr">
+        <is>
+          <t>Perche': Oggi il Piano di successione copre circa meta' dei ruoli critici: e' la lacuna principale del rischio.</t>
+        </is>
+      </c>
+      <c r="B52" s="48" t="n"/>
+      <c r="C52" s="48" t="n"/>
+      <c r="D52" s="48" t="n"/>
+      <c r="E52" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: Ogni ruolo critico con un sostituto formato; i ruoli senza sostituto (KRI di esposizione) devono scendere sotto la soglia di attenzione.</t>
+        </is>
+      </c>
+      <c r="F52" s="48" t="n"/>
+      <c r="G52" s="48" t="n"/>
+      <c r="H52" s="48" t="n"/>
+    </row>
+    <row r="53" ht="18.5" customHeight="1">
+      <c r="A53" s="45" t="inlineStr">
+        <is>
+          <t>• Definire i servizi minimi IT garantiti in caso di sciopero, d'intesa con le rappresentanze.</t>
+        </is>
+      </c>
+      <c r="F53" s="46" t="inlineStr">
+        <is>
+          <t>Direzione Sistemi Informativi</t>
+        </is>
+      </c>
+      <c r="H53" s="46" t="inlineStr">
+        <is>
+          <t>3 mesi · Approvata (ciclo 2026Q4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="32" customHeight="1">
+      <c r="A54" s="47" t="inlineStr">
+        <is>
+          <t>Perche': Senza servizi minimi concordati un'astensione puo' fermare processi critici o imporre turni non conformi.</t>
+        </is>
+      </c>
+      <c r="B54" s="48" t="n"/>
+      <c r="C54" s="48" t="n"/>
+      <c r="D54" s="48" t="n"/>
+      <c r="E54" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: Un danno minore in caso di sciopero (Impatto) e turni di copertura conformi agli obblighi di lavoro.</t>
+        </is>
+      </c>
+      <c r="F54" s="48" t="n"/>
+      <c r="G54" s="48" t="n"/>
+      <c r="H54" s="48" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="23" t="inlineStr">
+        <is>
+          <t>KRI in vigore</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="n"/>
+      <c r="C56" s="24" t="n"/>
+      <c r="D56" s="24" t="n"/>
+      <c r="E56" s="24" t="n"/>
+      <c r="F56" s="24" t="n"/>
+      <c r="G56" s="24" t="n"/>
+      <c r="H56" s="24" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="49" t="inlineStr">
+        <is>
+          <t>Indicatore</t>
+        </is>
+      </c>
+      <c r="E57" s="49" t="inlineStr">
+        <is>
+          <t>Valore</t>
+        </is>
+      </c>
+      <c r="F57" s="49" t="inlineStr">
+        <is>
+          <t>Soglie (attenzione / allerta)</t>
+        </is>
+      </c>
+      <c r="G57" s="49" t="inlineStr">
+        <is>
+          <t>Ciclo prima</t>
+        </is>
+      </c>
+      <c r="H57" s="49" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="50" t="inlineStr">
+        <is>
+          <t>[Esposizione] Ruoli IT critici senza sostituto formato (n)</t>
+        </is>
+      </c>
+      <c r="E58" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F58" s="52" t="inlineStr">
+        <is>
+          <t>3,0 / 6,0</t>
+        </is>
+      </c>
+      <c r="G58" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="63" t="inlineStr">
+        <is>
+          <t>Non rilevato</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
       <c r="A59" s="47" t="inlineStr">
         <is>
-          <t>Perche': La sostituzione (2026Q2-NFR-11-A1) e' un programma pluriennale e l'isolamento (2026Q3-NFR-11-A1) non corregge le vulnerabilita': il supporto esteso riporta le patch sulle componenti piu' esposte.</t>
+          <t>Perche' lo misuriamo: Misura quanto la Banca e' esposta: ogni ruolo critico senza sostituto e' un punto di blocco.</t>
         </is>
       </c>
       <c r="B59" s="48" t="n"/>
@@ -6229,196 +6474,114 @@
       <c r="D59" s="48" t="n"/>
       <c r="E59" s="47" t="inlineStr">
         <is>
-          <t>Effetto atteso: Il numero di componenti senza patch (NFR-11-K1) inizia a scendere; il rischio resta urgente finche' il programma non e' avanzato.</t>
+          <t>Effetto atteso: In calo con l'estensione del piano di successione, fino a zero.</t>
         </is>
       </c>
       <c r="F59" s="48" t="n"/>
       <c r="G59" s="48" t="n"/>
       <c r="H59" s="48" t="n"/>
     </row>
-    <row r="61">
-      <c r="A61" s="23" t="inlineStr">
-        <is>
-          <t>KRI in vigore</t>
-        </is>
-      </c>
-      <c r="B61" s="24" t="n"/>
-      <c r="C61" s="24" t="n"/>
-      <c r="D61" s="24" t="n"/>
-      <c r="E61" s="24" t="n"/>
-      <c r="F61" s="24" t="n"/>
-      <c r="G61" s="24" t="n"/>
-      <c r="H61" s="24" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="49" t="inlineStr">
-        <is>
-          <t>Indicatore</t>
-        </is>
-      </c>
-      <c r="E62" s="49" t="inlineStr">
-        <is>
-          <t>Valore</t>
-        </is>
-      </c>
-      <c r="F62" s="49" t="inlineStr">
-        <is>
-          <t>Soglie (attenzione / allerta)</t>
-        </is>
-      </c>
-      <c r="G62" s="49" t="inlineStr">
-        <is>
-          <t>Ciclo prima</t>
-        </is>
-      </c>
-      <c r="H62" s="49" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="50" t="inlineStr">
-        <is>
-          <t>[Esposizione] Componenti del sistema di pagamento fuori supporto (n)</t>
-        </is>
-      </c>
-      <c r="E63" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="F63" s="52" t="inlineStr">
-        <is>
-          <t>3,0 / 8,0</t>
-        </is>
-      </c>
-      <c r="G63" s="52" t="n">
-        <v>6</v>
-      </c>
-      <c r="H63" s="57" t="inlineStr">
-        <is>
-          <t>Ambra</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="47" t="inlineStr">
-        <is>
-          <t>Perche' lo misuriamo: Misura quanta parte del sistema di pagamento e' senza supporto: e' l'esposizione della Banca.</t>
-        </is>
-      </c>
-      <c r="B64" s="48" t="n"/>
-      <c r="C64" s="48" t="n"/>
-      <c r="D64" s="48" t="n"/>
-      <c r="E64" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: In calo con il piano di sostituzione; se sale, altre componenti sono uscite dal supporto.</t>
-        </is>
-      </c>
-      <c r="F64" s="48" t="n"/>
-      <c r="G64" s="48" t="n"/>
-      <c r="H64" s="48" t="n"/>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="50" t="inlineStr">
-        <is>
-          <t>[Evoluzione] Vulnerabilita' senza patch disponibile sui sistemi legacy (n)</t>
-        </is>
-      </c>
-      <c r="E65" s="51" t="n">
-        <v>6</v>
-      </c>
-      <c r="F65" s="52" t="inlineStr">
-        <is>
-          <t>2,0 / 6,0</t>
-        </is>
-      </c>
-      <c r="G65" s="52" t="n">
-        <v>5</v>
-      </c>
-      <c r="H65" s="53" t="inlineStr">
-        <is>
-          <t>Rosso</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="47" t="inlineStr">
-        <is>
-          <t>Perche' lo misuriamo: Misura quanto cresce la minaccia sulle componenti senza supporto.</t>
-        </is>
-      </c>
-      <c r="B66" s="48" t="n"/>
-      <c r="C66" s="48" t="n"/>
-      <c r="D66" s="48" t="n"/>
-      <c r="E66" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: Cresce nel tempo finche' le componenti restano; oltre la soglia di allerta servono subito misure compensative.</t>
-        </is>
-      </c>
-      <c r="F66" s="48" t="n"/>
-      <c r="G66" s="48" t="n"/>
-      <c r="H66" s="48" t="n"/>
-    </row>
-    <row r="68" ht="61" customHeight="1">
-      <c r="A68" s="15" t="inlineStr">
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="50" t="inlineStr">
+        <is>
+          <t>[Evoluzione] Turnover volontario annualizzato del personale IT (%)</t>
+        </is>
+      </c>
+      <c r="E60" s="51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F60" s="52" t="inlineStr">
+        <is>
+          <t>8,0 / 12,0</t>
+        </is>
+      </c>
+      <c r="G60" s="52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H60" s="63" t="inlineStr">
+        <is>
+          <t>Non rilevato</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="32" customHeight="1">
+      <c r="A61" s="47" t="inlineStr">
+        <is>
+          <t>Perche' lo misuriamo: Misura quanto cresce la perdita di competenze tecniche.</t>
+        </is>
+      </c>
+      <c r="B61" s="48" t="n"/>
+      <c r="C61" s="48" t="n"/>
+      <c r="D61" s="48" t="n"/>
+      <c r="E61" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: Stabile sotto la soglia di attenzione; oltre la soglia di allerta il rischio si avvicina e la Prossimita' va rivista.</t>
+        </is>
+      </c>
+      <c r="F61" s="48" t="n"/>
+      <c r="G61" s="48" t="n"/>
+      <c r="H61" s="48" t="n"/>
+    </row>
+    <row r="63" ht="61" customHeight="1">
+      <c r="A63" s="15" t="inlineStr">
         <is>
           <t>Legenda — Imp = Impatto, Prob = Probabilita, Pross = Prossimita, Vel = Velocity (1-5, 5 = peggiore; n.v. = non valutata, nessuna fonte ne documenta i tempi). Rilevanza di una fonte per la previsione: Alta = fonte primaria o caso documentato, Media = fonte specializzata, Bassa = generalista. Presidio = giudizio della Banca sui controlli, fuori dallo score. X = anni per decidere e avviare la mitigazione; Y = anni per mitigare (azioni o adeguamento strutturale); Z = anni prima che il rischio possa manifestarsi; AGIRE ORA = X + Y &gt; Z. Livello di allerta (calcolato dal registro): Attivazione = almeno due fra AGIRE ORA, KRI in rosso, notizie in peggioramento; Attenzione = uno di questi, o margine sotto l'anno con P x I alto, presidio assente o KRI in ambra; Monitoraggio = gli altri. KRI = indicatore di rischio, di esposizione (quanto la Banca e' esposta) o di evoluzione (quanto cresce il fenomeno). ◆ = tema all'attenzione del supervisore.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="47">
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="C16:H16"/>
+    <mergeCell ref="E61:H61"/>
     <mergeCell ref="G2:H2"/>
-    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="A46:C46"/>
     <mergeCell ref="A24:H24"/>
-    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="E54:H54"/>
     <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A49:H49"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="C12:H12"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="A61:H61"/>
     <mergeCell ref="A6:H6"/>
-    <mergeCell ref="E66:H66"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="F51:G51"/>
     <mergeCell ref="A59:D59"/>
-    <mergeCell ref="E55:H55"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="E52:H52"/>
+    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A26:H26"/>
     <mergeCell ref="A21:H21"/>
-    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="A61:D61"/>
     <mergeCell ref="C13:H13"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="G45:H45"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A48:C48"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="A66:D66"/>
     <mergeCell ref="A17:H17"/>
     <mergeCell ref="C15:H15"/>
-    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A53:E53"/>
     <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A45:C45"/>
     <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="G47:H47"/>
+    <mergeCell ref="A63:H63"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="A57:D57"/>
     <mergeCell ref="E59:H59"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="G46:H46"/>
     <mergeCell ref="C3:D3"/>
     <mergeCell ref="E3:F3"/>
+    <mergeCell ref="F53:G53"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -6481,7 +6644,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>L1-01 · Frode interna</t>
+          <t>9.7 · Sicurezza informatica</t>
         </is>
       </c>
       <c r="B3" s="21" t="n"/>
@@ -6603,7 +6766,7 @@
           <t>Probabilita</t>
         </is>
       </c>
-      <c r="B14" s="58" t="n">
+      <c r="B14" s="59" t="n">
         <v>2</v>
       </c>
       <c r="C14" s="29" t="inlineStr">
@@ -6679,7 +6842,7 @@
       <c r="H19" s="24" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>Livello di allerta: Monitoraggio — nessun segnale forte.</t>
         </is>
@@ -6768,7 +6931,7 @@
       <c r="B28" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="C28" s="60" t="n">
+      <c r="C28" s="57" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="35" t="n">
@@ -6790,7 +6953,7 @@
       <c r="B29" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="C29" s="60" t="n">
+      <c r="C29" s="57" t="n">
         <v>2</v>
       </c>
       <c r="D29" s="35" t="n">
@@ -6812,7 +6975,7 @@
       <c r="B30" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="C30" s="60" t="n">
+      <c r="C30" s="57" t="n">
         <v>2</v>
       </c>
       <c r="D30" s="35" t="n">
@@ -6834,7 +6997,7 @@
       <c r="B31" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="C31" s="60" t="n">
+      <c r="C31" s="57" t="n">
         <v>2</v>
       </c>
       <c r="D31" s="35" t="n">
@@ -6856,7 +7019,7 @@
       <c r="B32" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="60" t="n">
+      <c r="C32" s="57" t="n">
         <v>2</v>
       </c>
       <c r="D32" s="35" t="n">
@@ -7300,7 +7463,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>L1-02 · Frode esterna</t>
+          <t>9.7 · Sicurezza informatica</t>
         </is>
       </c>
       <c r="B3" s="21" t="n"/>
@@ -8272,1726 +8435,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>Horizon Scan NFR — schede dei rischi · ciclo 2026Q4 · dati al 31/12/2026 · validato · Uso interno</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>2 · NFR-07 · Ransomware presso un fornitore di servizi di pagamento</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="n"/>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="18" t="n"/>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="19" t="inlineStr">
-        <is>
-          <t>score 3,75   ● 0,00   ·   Entro l'anno   ·   Attenzione</t>
-        </is>
-      </c>
-      <c r="H2" s="18" t="n"/>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>L1-06 · Interruzione dell'operativita' e disfunzione dei sistemi</t>
-        </is>
-      </c>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>Driver: DRV-CYB, DRV-TPR</t>
-        </is>
-      </c>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>Owner: Funzione ICT &amp; Security Risk · Presidio: Parziale</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="n"/>
-      <c r="G3" s="22" t="inlineStr">
-        <is>
-          <t>◆ Attenzione del supervisore</t>
-        </is>
-      </c>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>Esito: Confermato · validato</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>Il rischio</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="24" t="n"/>
-      <c r="H5" s="24" t="n"/>
-    </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>Blocco prolungato dei pagamenti per un attacco ransomware al fornitore esterno che gestisce il gateway di pagamento della Banca.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>Razionale: il fenomeno in termini di rischio</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="n"/>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="24" t="n"/>
-      <c r="H8" s="24" t="n"/>
-    </row>
-    <row r="9" ht="33" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>I gruppi ransomware colpiscono sempre piu' i fornitori che servono molte banche (causa); un attacco al fornitore del gateway di pagamento (evento) blocca i pagamenti della Banca finche' il fornitore non ripristina i sistemi, con danno ai clienti, sanzioni e reputazione (danno). Nessuna evidenza nuova nel trimestre: valori confermati.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>Valutazione, dimensione per dimensione (valori validati)</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="24" t="n"/>
-      <c r="H11" s="24" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>Dimensione</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>Valore</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>Perche' questo valore: informazioni e documenti</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>Impatto</t>
-        </is>
-      </c>
-      <c r="B13" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="29" t="inlineStr">
-        <is>
-          <t>Grave. Il Registro DORA classifica critico il fornitore del gateway: il blocco interrompe una funzione essenziale.</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>Probabilita</t>
-        </is>
-      </c>
-      <c r="B14" s="55" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="29" t="inlineStr">
-        <is>
-          <t>Possibile. L'attacco ransomware a un processore di pagamenti europeo e' un caso nel settore; la Banca e' esposta perche' dipende da un solo gateway.</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>Prossimita</t>
-        </is>
-      </c>
-      <c r="B15" s="55" t="n">
-        <v>3</v>
-      </c>
-      <c r="C15" s="29" t="inlineStr">
-        <is>
-          <t>Da uno a due anni. Nessun attacco o segnale specifico sul fornitore della Banca.</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>Velocity</t>
-        </is>
-      </c>
-      <c r="B16" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>Entro un mese. Nell'attacco al processore di pagamenti europeo i pagamenti si sono fermati il giorno stesso.</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>Score composito 3,75 = (0,35 x 4 + 0,25 x 3 + 0,20 x 3 + 0,20 x 5) / 1,00. La rilevanza delle fonti e' nella tabella Fonti.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
-        <is>
-          <t>Urgenza (disuguaglianza di Mosca) e livello di allerta</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="24" t="n"/>
-      <c r="H19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="56" t="inlineStr">
-        <is>
-          <t>Livello di allerta: Attenzione — margine sotto l'anno con P x I alta, KRI in ambra o rosso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>Agire entro l'anno. Tempo necessario X + Y = 0,25 + 0,50 = 0,75 anni; tempo disponibile Z = 1,5 anni (Prossimita 3). Margine Z - (X + Y) = 0,75.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>Cosa e' cambiato nel ciclo</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="n"/>
-      <c r="C23" s="24" t="n"/>
-      <c r="D23" s="24" t="n"/>
-      <c r="E23" s="24" t="n"/>
-      <c r="F23" s="24" t="n"/>
-      <c r="G23" s="24" t="n"/>
-      <c r="H23" s="24" t="n"/>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>Nessun valore cambiato: confermato sulle fonti del ciclo precedente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>Andamento negli ultimi trimestri</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="24" t="n"/>
-      <c r="F26" s="24" t="n"/>
-      <c r="G26" s="24" t="n"/>
-      <c r="H26" s="24" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="33" t="inlineStr">
-        <is>
-          <t>Ciclo</t>
-        </is>
-      </c>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t>Imp</t>
-        </is>
-      </c>
-      <c r="C27" s="33" t="inlineStr">
-        <is>
-          <t>Prob</t>
-        </is>
-      </c>
-      <c r="D27" s="33" t="inlineStr">
-        <is>
-          <t>Pross</t>
-        </is>
-      </c>
-      <c r="E27" s="33" t="inlineStr">
-        <is>
-          <t>Vel</t>
-        </is>
-      </c>
-      <c r="F27" s="33" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="34" t="inlineStr">
-        <is>
-          <t>2025Q4</t>
-        </is>
-      </c>
-      <c r="B28" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="C28" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F28" s="37" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="34" t="inlineStr">
-        <is>
-          <t>2026Q1</t>
-        </is>
-      </c>
-      <c r="B29" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="C29" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D29" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F29" s="37" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="34" t="inlineStr">
-        <is>
-          <t>2026Q2</t>
-        </is>
-      </c>
-      <c r="B30" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="C30" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D30" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E30" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F30" s="37" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="34" t="inlineStr">
-        <is>
-          <t>2026Q3</t>
-        </is>
-      </c>
-      <c r="B31" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D31" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F31" s="37" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="34" t="inlineStr">
-        <is>
-          <t>2026Q4</t>
-        </is>
-      </c>
-      <c r="B32" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="C32" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="D32" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E32" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="F32" s="37" t="n">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="23" t="inlineStr">
-        <is>
-          <t>Fonti</t>
-        </is>
-      </c>
-      <c r="B47" s="24" t="n"/>
-      <c r="C47" s="24" t="n"/>
-      <c r="D47" s="24" t="n"/>
-      <c r="E47" s="24" t="n"/>
-      <c r="F47" s="24" t="n"/>
-      <c r="G47" s="24" t="n"/>
-      <c r="H47" s="24" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="26" t="inlineStr">
-        <is>
-          <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D48" s="26" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="E48" s="26" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="F48" s="26" t="inlineStr">
-        <is>
-          <t>Rilevanza</t>
-        </is>
-      </c>
-      <c r="G48" s="26" t="n"/>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="39" t="inlineStr">
-        <is>
-          <t>Registro DORA: fornitore del gateway di pagamento classificato critico</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="40" t="inlineStr">
-        <is>
-          <t>15/10/2025</t>
-        </is>
-      </c>
-      <c r="E49" s="41" t="inlineStr">
-        <is>
-          <t>Interna</t>
-        </is>
-      </c>
-      <c r="F49" s="42" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="G49" s="39" t="n"/>
-      <c r="H49" s="6" t="n"/>
-    </row>
-    <row r="50" ht="18.5" customHeight="1">
-      <c r="A50" s="39" t="inlineStr">
-        <is>
-          <t>Attacco ransomware a un processore di pagamenti europeo</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="40" t="inlineStr">
-        <is>
-          <t>20/02/2026</t>
-        </is>
-      </c>
-      <c r="E50" s="43" t="inlineStr">
-        <is>
-          <t>Esterna</t>
-        </is>
-      </c>
-      <c r="F50" s="42" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="G50" s="39" t="n"/>
-      <c r="H50" s="6" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="23" t="inlineStr">
-        <is>
-          <t>Azioni</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="n"/>
-      <c r="C52" s="24" t="n"/>
-      <c r="D52" s="24" t="n"/>
-      <c r="E52" s="24" t="n"/>
-      <c r="F52" s="24" t="n"/>
-      <c r="G52" s="24" t="n"/>
-      <c r="H52" s="24" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="26" t="inlineStr">
-        <is>
-          <t>Azione</t>
-        </is>
-      </c>
-      <c r="F53" s="26" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="H53" s="26" t="inlineStr">
-        <is>
-          <t>Orizzonte · stato</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18.5" customHeight="1">
-      <c r="A54" s="45" t="inlineStr">
-        <is>
-          <t>• Test congiunto di ripristino da ransomware con il fornitore del gateway di pagamento.</t>
-        </is>
-      </c>
-      <c r="F54" s="46" t="inlineStr">
-        <is>
-          <t>Funzione ICT &amp; Security Risk</t>
-        </is>
-      </c>
-      <c r="H54" s="46" t="inlineStr">
-        <is>
-          <t>6 mesi · Approvata (ciclo 2026Q2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="A55" s="47" t="inlineStr">
-        <is>
-          <t>Perche': Il ripristino da ransomware non e' mai stato testato con il fornitore.</t>
-        </is>
-      </c>
-      <c r="B55" s="48" t="n"/>
-      <c r="C55" s="48" t="n"/>
-      <c r="D55" s="48" t="n"/>
-      <c r="E55" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: non indicato nel razionale di A1.</t>
-        </is>
-      </c>
-      <c r="F55" s="48" t="n"/>
-      <c r="G55" s="48" t="n"/>
-      <c r="H55" s="48" t="n"/>
-    </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="45" t="inlineStr">
-        <is>
-          <t>• Inserire nel contratto con il fornitore del gateway di pagamento tempi di ripristino garantiti dopo un attacco ransomware, con penali.</t>
-        </is>
-      </c>
-      <c r="F56" s="46" t="inlineStr">
-        <is>
-          <t>Funzione ICT &amp; Security Risk</t>
-        </is>
-      </c>
-      <c r="H56" s="46" t="inlineStr">
-        <is>
-          <t>6 mesi · Approvata (ciclo 2026Q3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="47" t="inlineStr">
-        <is>
-          <t>Perche': Il test congiunto di ripristino (2026Q2-NFR-07-A1) misura i tempi; il contratto li rende vincolanti per il fornitore.</t>
-        </is>
-      </c>
-      <c r="B57" s="48" t="n"/>
-      <c r="C57" s="48" t="n"/>
-      <c r="D57" s="48" t="n"/>
-      <c r="E57" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: non indicato nel razionale di A1.</t>
-        </is>
-      </c>
-      <c r="F57" s="48" t="n"/>
-      <c r="G57" s="48" t="n"/>
-      <c r="H57" s="48" t="n"/>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="45" t="inlineStr">
-        <is>
-          <t>• Prevedere un canale di pagamento alternativo, attivabile entro 24 ore, se il gateway del fornitore resta bloccato da un attacco.</t>
-        </is>
-      </c>
-      <c r="F58" s="46" t="inlineStr">
-        <is>
-          <t>Funzione ICT &amp; Security Risk</t>
-        </is>
-      </c>
-      <c r="H58" s="46" t="inlineStr">
-        <is>
-          <t>6 mesi · Approvata (ciclo 2026Q4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="32" customHeight="1">
-      <c r="A59" s="47" t="inlineStr">
-        <is>
-          <t>Perche': Il test di ripristino (2026Q2-NFR-07-A1) e i tempi contrattuali (2026Q3-NFR-07-A1) non coprono un blocco lungo del fornitore: serve un'alternativa.</t>
-        </is>
-      </c>
-      <c r="B59" s="48" t="n"/>
-      <c r="C59" s="48" t="n"/>
-      <c r="D59" s="48" t="n"/>
-      <c r="E59" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: Un blocco del fornitore non ferma i pagamenti per piu' di un giorno, quindi un danno contenuto anche nel caso peggiore.</t>
-        </is>
-      </c>
-      <c r="F59" s="48" t="n"/>
-      <c r="G59" s="48" t="n"/>
-      <c r="H59" s="48" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="23" t="inlineStr">
-        <is>
-          <t>KRI in vigore</t>
-        </is>
-      </c>
-      <c r="B61" s="24" t="n"/>
-      <c r="C61" s="24" t="n"/>
-      <c r="D61" s="24" t="n"/>
-      <c r="E61" s="24" t="n"/>
-      <c r="F61" s="24" t="n"/>
-      <c r="G61" s="24" t="n"/>
-      <c r="H61" s="24" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="49" t="inlineStr">
-        <is>
-          <t>Indicatore</t>
-        </is>
-      </c>
-      <c r="E62" s="49" t="inlineStr">
-        <is>
-          <t>Valore</t>
-        </is>
-      </c>
-      <c r="F62" s="49" t="inlineStr">
-        <is>
-          <t>Soglie (attenzione / allerta)</t>
-        </is>
-      </c>
-      <c r="G62" s="49" t="inlineStr">
-        <is>
-          <t>Ciclo prima</t>
-        </is>
-      </c>
-      <c r="H62" s="49" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="50" t="inlineStr">
-        <is>
-          <t>[Esposizione] Fornitori di pagamento critici senza test di ripristino da ransomware (n)</t>
-        </is>
-      </c>
-      <c r="E63" s="51" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="52" t="inlineStr">
-        <is>
-          <t>1,0 / 2,0</t>
-        </is>
-      </c>
-      <c r="G63" s="52" t="n">
-        <v>1</v>
-      </c>
-      <c r="H63" s="57" t="inlineStr">
-        <is>
-          <t>Ambra</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="47" t="inlineStr">
-        <is>
-          <t>Perche' lo misuriamo: Misura quanto la Banca e' esposta: un fornitore critico mai provato nel ripristino e' un blocco di durata sconosciuta.</t>
-        </is>
-      </c>
-      <c r="B64" s="48" t="n"/>
-      <c r="C64" s="48" t="n"/>
-      <c r="D64" s="48" t="n"/>
-      <c r="E64" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: Atteso a zero dopo il test congiunto; ogni nuovo fornitore critico senza test lo riporta in ambra.</t>
-        </is>
-      </c>
-      <c r="F64" s="48" t="n"/>
-      <c r="G64" s="48" t="n"/>
-      <c r="H64" s="48" t="n"/>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="50" t="inlineStr">
-        <is>
-          <t>[Evoluzione] Ore di indisponibilita' del gateway di pagamento nel trimestre (ore)</t>
-        </is>
-      </c>
-      <c r="E65" s="51" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F65" s="52" t="inlineStr">
-        <is>
-          <t>4,0 / 12,0</t>
-        </is>
-      </c>
-      <c r="G65" s="52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H65" s="54" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="47" t="inlineStr">
-        <is>
-          <t>Perche' lo misuriamo: Misura le interruzioni reali del gateway, il canale attraverso cui il rischio colpisce.</t>
-        </is>
-      </c>
-      <c r="B66" s="48" t="n"/>
-      <c r="C66" s="48" t="n"/>
-      <c r="D66" s="48" t="n"/>
-      <c r="E66" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: Poche ore e stabili; oltre la soglia di allerta il fornitore ha problemi di continuita' e la Prossimita' va rivista.</t>
-        </is>
-      </c>
-      <c r="F66" s="48" t="n"/>
-      <c r="G66" s="48" t="n"/>
-      <c r="H66" s="48" t="n"/>
-    </row>
-    <row r="68" ht="61" customHeight="1">
-      <c r="A68" s="15" t="inlineStr">
-        <is>
-          <t>Legenda — Imp = Impatto, Prob = Probabilita, Pross = Prossimita, Vel = Velocity (1-5, 5 = peggiore; n.v. = non valutata, nessuna fonte ne documenta i tempi). Rilevanza di una fonte per la previsione: Alta = fonte primaria o caso documentato, Media = fonte specializzata, Bassa = generalista. Presidio = giudizio della Banca sui controlli, fuori dallo score. X = anni per decidere e avviare la mitigazione; Y = anni per mitigare (azioni o adeguamento strutturale); Z = anni prima che il rischio possa manifestarsi; AGIRE ORA = X + Y &gt; Z. Livello di allerta (calcolato dal registro): Attivazione = almeno due fra AGIRE ORA, KRI in rosso, notizie in peggioramento; Attenzione = uno di questi, o margine sotto l'anno con P x I alto, presidio assente o KRI in ambra; Monitoraggio = gli altri. KRI = indicatore di rischio, di esposizione (quanto la Banca e' esposta) o di evoluzione (quanto cresce il fenomeno). ◆ = tema all'attenzione del supervisore.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-  </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CUso interno&amp;RHorizon Scan NFR</oddHeader>
-    <oddFooter>&amp;L&amp;F · &amp;A&amp;RPagina &amp;P di &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H68"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="16" t="inlineStr">
-        <is>
-          <t>Horizon Scan NFR — schede dei rischi · ciclo 2026Q4 · dati al 31/12/2026 · validato · Uso interno</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>3 · NFR-12 · Errori operativi nei pagamenti istantanei obbligatori</t>
-        </is>
-      </c>
-      <c r="B2" s="18" t="n"/>
-      <c r="C2" s="18" t="n"/>
-      <c r="D2" s="18" t="n"/>
-      <c r="E2" s="18" t="n"/>
-      <c r="F2" s="18" t="n"/>
-      <c r="G2" s="19" t="inlineStr">
-        <is>
-          <t>score 3,65   ● 0,00   ·   Entro l'anno   ·   Attenzione</t>
-        </is>
-      </c>
-      <c r="H2" s="18" t="n"/>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="20" t="inlineStr">
-        <is>
-          <t>L1-07 · Esecuzione, consegna e gestione dei processi</t>
-        </is>
-      </c>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="20" t="inlineStr">
-        <is>
-          <t>Driver: DRV-TEC</t>
-        </is>
-      </c>
-      <c r="D3" s="21" t="n"/>
-      <c r="E3" s="20" t="inlineStr">
-        <is>
-          <t>Owner: Funzione Operations · Presidio: Parziale</t>
-        </is>
-      </c>
-      <c r="F3" s="21" t="n"/>
-      <c r="G3" s="20" t="n"/>
-      <c r="H3" s="20" t="inlineStr">
-        <is>
-          <t>Esito: Confermato · validato</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>Il rischio</t>
-        </is>
-      </c>
-      <c r="B5" s="24" t="n"/>
-      <c r="C5" s="24" t="n"/>
-      <c r="D5" s="24" t="n"/>
-      <c r="E5" s="24" t="n"/>
-      <c r="F5" s="24" t="n"/>
-      <c r="G5" s="24" t="n"/>
-      <c r="H5" s="24" t="n"/>
-    </row>
-    <row r="6" ht="19.5" customHeight="1">
-      <c r="A6" s="25" t="inlineStr">
-        <is>
-          <t>Errori di riconciliazione e rimborsi indebiti dopo l'obbligo di offrire i bonifici istantanei a tutta la clientela.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="inlineStr">
-        <is>
-          <t>Razionale: il fenomeno in termini di rischio</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="n"/>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="24" t="n"/>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="24" t="n"/>
-      <c r="H8" s="24" t="n"/>
-    </row>
-    <row r="9" ht="33" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>L'obbligo di offrire i bonifici istantanei a tutta la clientela moltiplica i volumi da riconciliare in tempo reale (causa); differenze di riconciliazione non risolte ed eccezioni portano a rimborsi indebiti o pagamenti errati (evento); la Banca subisce perdite operative e reclami (danno). Nessuna evidenza nuova nel trimestre: valori confermati.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>Valutazione, dimensione per dimensione (valori validati)</t>
-        </is>
-      </c>
-      <c r="B11" s="24" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="24" t="n"/>
-      <c r="E11" s="24" t="n"/>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="24" t="n"/>
-      <c r="H11" s="24" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>Dimensione</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>Valore</t>
-        </is>
-      </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>Perche' questo valore: informazioni e documenti</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="33" customHeight="1">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>Impatto</t>
-        </is>
-      </c>
-      <c r="B13" s="55" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="29" t="inlineStr">
-        <is>
-          <t>Rilevante. Il Piano di adeguamento al regolamento sui bonifici istantanei estende il servizio a tutta la clientela: un errore tocca una clientela ampia.</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>Probabilita</t>
-        </is>
-      </c>
-      <c r="B14" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="C14" s="29" t="inlineStr">
-        <is>
-          <t>Probabile. Il Report operativo dei pagamenti istantanei di maggio documenta differenze di riconciliazione in crescita presso la Banca.</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="27" t="inlineStr">
-        <is>
-          <t>Prossimita</t>
-        </is>
-      </c>
-      <c r="B15" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="C15" s="29" t="inlineStr">
-        <is>
-          <t>Entro dodici mesi. Le differenze aperte del Report operativo sono quasi-incidenti gia' documentati presso la Banca.</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="27" t="inlineStr">
-        <is>
-          <t>Velocity</t>
-        </is>
-      </c>
-      <c r="B16" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>Da uno a tre mesi. Con la riconciliazione settimanale le differenze si accumulano in poche settimane (Report operativo).</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="31" t="inlineStr">
-        <is>
-          <t>Score composito 3,65 = (0,35 x 3 + 0,25 x 4 + 0,20 x 4 + 0,20 x 4) / 1,00. La rilevanza delle fonti e' nella tabella Fonti.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="inlineStr">
-        <is>
-          <t>Urgenza (disuguaglianza di Mosca) e livello di allerta</t>
-        </is>
-      </c>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="24" t="n"/>
-      <c r="E19" s="24" t="n"/>
-      <c r="F19" s="24" t="n"/>
-      <c r="G19" s="24" t="n"/>
-      <c r="H19" s="24" t="n"/>
-    </row>
-    <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="56" t="inlineStr">
-        <is>
-          <t>Livello di allerta: Attenzione — margine sotto l'anno con P x I alta, KRI in ambra o rosso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="19.5" customHeight="1">
-      <c r="A21" s="25" t="inlineStr">
-        <is>
-          <t>Agire entro l'anno. Tempo necessario X + Y = 0,25 + 0,25 = 0,50 anni; tempo disponibile Z = 0,5 anni (Prossimita 4). Margine Z - (X + Y) = 0,00.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>Cosa e' cambiato nel ciclo</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="n"/>
-      <c r="C23" s="24" t="n"/>
-      <c r="D23" s="24" t="n"/>
-      <c r="E23" s="24" t="n"/>
-      <c r="F23" s="24" t="n"/>
-      <c r="G23" s="24" t="n"/>
-      <c r="H23" s="24" t="n"/>
-    </row>
-    <row r="24" ht="19.5" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
-        <is>
-          <t>Nessun valore cambiato: confermato sulle fonti del ciclo precedente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="23" t="inlineStr">
-        <is>
-          <t>Andamento negli ultimi trimestri</t>
-        </is>
-      </c>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="24" t="n"/>
-      <c r="F26" s="24" t="n"/>
-      <c r="G26" s="24" t="n"/>
-      <c r="H26" s="24" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="33" t="inlineStr">
-        <is>
-          <t>Ciclo</t>
-        </is>
-      </c>
-      <c r="B27" s="33" t="inlineStr">
-        <is>
-          <t>Imp</t>
-        </is>
-      </c>
-      <c r="C27" s="33" t="inlineStr">
-        <is>
-          <t>Prob</t>
-        </is>
-      </c>
-      <c r="D27" s="33" t="inlineStr">
-        <is>
-          <t>Pross</t>
-        </is>
-      </c>
-      <c r="E27" s="33" t="inlineStr">
-        <is>
-          <t>Vel</t>
-        </is>
-      </c>
-      <c r="F27" s="33" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="34" t="inlineStr">
-        <is>
-          <t>2025Q4</t>
-        </is>
-      </c>
-      <c r="B28" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D28" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E28" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="F28" s="37" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="34" t="inlineStr">
-        <is>
-          <t>2026Q1</t>
-        </is>
-      </c>
-      <c r="B29" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C29" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D29" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="E29" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="F29" s="37" t="n">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="34" t="inlineStr">
-        <is>
-          <t>2026Q2</t>
-        </is>
-      </c>
-      <c r="B30" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C30" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D30" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E30" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="F30" s="37" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="34" t="inlineStr">
-        <is>
-          <t>2026Q3</t>
-        </is>
-      </c>
-      <c r="B31" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C31" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D31" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E31" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="F31" s="37" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="34" t="inlineStr">
-        <is>
-          <t>2026Q4</t>
-        </is>
-      </c>
-      <c r="B32" s="35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D32" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E32" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="F32" s="37" t="n">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="23" t="inlineStr">
-        <is>
-          <t>Fonti</t>
-        </is>
-      </c>
-      <c r="B47" s="24" t="n"/>
-      <c r="C47" s="24" t="n"/>
-      <c r="D47" s="24" t="n"/>
-      <c r="E47" s="24" t="n"/>
-      <c r="F47" s="24" t="n"/>
-      <c r="G47" s="24" t="n"/>
-      <c r="H47" s="24" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="26" t="inlineStr">
-        <is>
-          <t>Fonte</t>
-        </is>
-      </c>
-      <c r="D48" s="26" t="inlineStr">
-        <is>
-          <t>Data</t>
-        </is>
-      </c>
-      <c r="E48" s="26" t="inlineStr">
-        <is>
-          <t>Tipo</t>
-        </is>
-      </c>
-      <c r="F48" s="26" t="inlineStr">
-        <is>
-          <t>Rilevanza</t>
-        </is>
-      </c>
-      <c r="G48" s="26" t="n"/>
-    </row>
-    <row r="49" ht="32" customHeight="1">
-      <c r="A49" s="39" t="inlineStr">
-        <is>
-          <t>Piano di adeguamento al regolamento sui bonifici istantanei</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n"/>
-      <c r="C49" s="6" t="n"/>
-      <c r="D49" s="40" t="inlineStr">
-        <is>
-          <t>01/10/2025</t>
-        </is>
-      </c>
-      <c r="E49" s="41" t="inlineStr">
-        <is>
-          <t>Interna</t>
-        </is>
-      </c>
-      <c r="F49" s="42" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="G49" s="39" t="n"/>
-      <c r="H49" s="6" t="n"/>
-    </row>
-    <row r="50" ht="18.5" customHeight="1">
-      <c r="A50" s="39" t="inlineStr">
-        <is>
-          <t>Report operativo dei pagamenti istantanei — maggio</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="n"/>
-      <c r="C50" s="6" t="n"/>
-      <c r="D50" s="40" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="E50" s="41" t="inlineStr">
-        <is>
-          <t>Interna</t>
-        </is>
-      </c>
-      <c r="F50" s="42" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="G50" s="39" t="n"/>
-      <c r="H50" s="6" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="23" t="inlineStr">
-        <is>
-          <t>Azioni</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="n"/>
-      <c r="C52" s="24" t="n"/>
-      <c r="D52" s="24" t="n"/>
-      <c r="E52" s="24" t="n"/>
-      <c r="F52" s="24" t="n"/>
-      <c r="G52" s="24" t="n"/>
-      <c r="H52" s="24" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="26" t="inlineStr">
-        <is>
-          <t>Azione</t>
-        </is>
-      </c>
-      <c r="F53" s="26" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="H53" s="26" t="inlineStr">
-        <is>
-          <t>Orizzonte · stato</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18.5" customHeight="1">
-      <c r="A54" s="45" t="inlineStr">
-        <is>
-          <t>• Controllo giornaliero automatico delle differenze di riconciliazione sui bonifici istantanei.</t>
-        </is>
-      </c>
-      <c r="F54" s="46" t="inlineStr">
-        <is>
-          <t>Funzione Operations</t>
-        </is>
-      </c>
-      <c r="H54" s="46" t="inlineStr">
-        <is>
-          <t>3 mesi · Approvata (ciclo 2026Q2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="19" customHeight="1">
-      <c r="A55" s="47" t="inlineStr">
-        <is>
-          <t>Perche': La riconciliazione oggi e' settimanale: gli errori emergono troppo tardi.</t>
-        </is>
-      </c>
-      <c r="B55" s="48" t="n"/>
-      <c r="C55" s="48" t="n"/>
-      <c r="D55" s="48" t="n"/>
-      <c r="E55" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: non indicato nel razionale di A1.</t>
-        </is>
-      </c>
-      <c r="F55" s="48" t="n"/>
-      <c r="G55" s="48" t="n"/>
-      <c r="H55" s="48" t="n"/>
-    </row>
-    <row r="56" ht="32" customHeight="1">
-      <c r="A56" s="45" t="inlineStr">
-        <is>
-          <t>• Avvisare in automatico il responsabile delle operazioni di ogni differenza di riconciliazione sui bonifici istantanei aperta a fine giornata.</t>
-        </is>
-      </c>
-      <c r="F56" s="46" t="inlineStr">
-        <is>
-          <t>Funzione Operations</t>
-        </is>
-      </c>
-      <c r="H56" s="46" t="inlineStr">
-        <is>
-          <t>3 mesi · Approvata (ciclo 2026Q3)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="32" customHeight="1">
-      <c r="A57" s="47" t="inlineStr">
-        <is>
-          <t>Perche': Il controllo giornaliero (2026Q2-NFR-12-A1) trova le differenze; l'avviso porta a chi decide quelle non chiuse in giornata.</t>
-        </is>
-      </c>
-      <c r="B57" s="48" t="n"/>
-      <c r="C57" s="48" t="n"/>
-      <c r="D57" s="48" t="n"/>
-      <c r="E57" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: non indicato nel razionale di A1.</t>
-        </is>
-      </c>
-      <c r="F57" s="48" t="n"/>
-      <c r="G57" s="48" t="n"/>
-      <c r="H57" s="48" t="n"/>
-    </row>
-    <row r="58" ht="32" customHeight="1">
-      <c r="A58" s="45" t="inlineStr">
-        <is>
-          <t>• Introdurre un test di riconciliazione su dati anonimizzati prima di ogni rilascio del motore dei bonifici istantanei.</t>
-        </is>
-      </c>
-      <c r="F58" s="46" t="inlineStr">
-        <is>
-          <t>Funzione Operations</t>
-        </is>
-      </c>
-      <c r="H58" s="46" t="inlineStr">
-        <is>
-          <t>3 mesi · Approvata (ciclo 2026Q4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
-      <c r="A59" s="47" t="inlineStr">
-        <is>
-          <t>Perche': Il controllo giornaliero (2026Q2-NFR-12-A1) e l'avviso (2026Q3-NFR-12-A1) trovano le differenze dopo; molte nascono dalle modifiche al software, che il test ferma prima.</t>
-        </is>
-      </c>
-      <c r="B59" s="48" t="n"/>
-      <c r="C59" s="48" t="n"/>
-      <c r="D59" s="48" t="n"/>
-      <c r="E59" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: Meno differenze dopo i rilasci; quelle aperte oltre un giorno (NFR-12-K1) scendono sotto la soglia di attenzione.</t>
-        </is>
-      </c>
-      <c r="F59" s="48" t="n"/>
-      <c r="G59" s="48" t="n"/>
-      <c r="H59" s="48" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="23" t="inlineStr">
-        <is>
-          <t>KRI in vigore</t>
-        </is>
-      </c>
-      <c r="B61" s="24" t="n"/>
-      <c r="C61" s="24" t="n"/>
-      <c r="D61" s="24" t="n"/>
-      <c r="E61" s="24" t="n"/>
-      <c r="F61" s="24" t="n"/>
-      <c r="G61" s="24" t="n"/>
-      <c r="H61" s="24" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="49" t="inlineStr">
-        <is>
-          <t>Indicatore</t>
-        </is>
-      </c>
-      <c r="E62" s="49" t="inlineStr">
-        <is>
-          <t>Valore</t>
-        </is>
-      </c>
-      <c r="F62" s="49" t="inlineStr">
-        <is>
-          <t>Soglie (attenzione / allerta)</t>
-        </is>
-      </c>
-      <c r="G62" s="49" t="inlineStr">
-        <is>
-          <t>Ciclo prima</t>
-        </is>
-      </c>
-      <c r="H62" s="49" t="inlineStr">
-        <is>
-          <t>Stato</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="50" t="inlineStr">
-        <is>
-          <t>[Evoluzione] Differenze di riconciliazione sui bonifici istantanei aperte oltre 1 giorno (n)</t>
-        </is>
-      </c>
-      <c r="E63" s="51" t="n">
-        <v>9</v>
-      </c>
-      <c r="F63" s="52" t="inlineStr">
-        <is>
-          <t>10,0 / 30,0</t>
-        </is>
-      </c>
-      <c r="G63" s="52" t="n">
-        <v>12</v>
-      </c>
-      <c r="H63" s="54" t="inlineStr">
-        <is>
-          <t>Verde</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="32" customHeight="1">
-      <c r="A64" s="47" t="inlineStr">
-        <is>
-          <t>Perche' lo misuriamo: Misura il fenomeno nel punto in cui produce perdite: le differenze che non si chiudono in giornata.</t>
-        </is>
-      </c>
-      <c r="B64" s="48" t="n"/>
-      <c r="C64" s="48" t="n"/>
-      <c r="D64" s="48" t="n"/>
-      <c r="E64" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: In calo con il controllo giornaliero; oltre la soglia di allerta la riconciliazione non regge i volumi.</t>
-        </is>
-      </c>
-      <c r="F64" s="48" t="n"/>
-      <c r="G64" s="48" t="n"/>
-      <c r="H64" s="48" t="n"/>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="50" t="inlineStr">
-        <is>
-          <t>[Esposizione] Tempo medio di risoluzione delle eccezioni sui pagamenti istantanei (ore)</t>
-        </is>
-      </c>
-      <c r="E65" s="51" t="n">
-        <v>4</v>
-      </c>
-      <c r="F65" s="52" t="inlineStr">
-        <is>
-          <t>4,0 / 12,0</t>
-        </is>
-      </c>
-      <c r="G65" s="52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H65" s="57" t="inlineStr">
-        <is>
-          <t>Ambra</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="47" t="inlineStr">
-        <is>
-          <t>Perche' lo misuriamo: Misura quanto a lungo la Banca resta esposta a un'eccezione aperta.</t>
-        </is>
-      </c>
-      <c r="B66" s="48" t="n"/>
-      <c r="C66" s="48" t="n"/>
-      <c r="D66" s="48" t="n"/>
-      <c r="E66" s="47" t="inlineStr">
-        <is>
-          <t>Effetto atteso: Sotto la soglia di attenzione quando il controllo giornaliero e' a regime.</t>
-        </is>
-      </c>
-      <c r="F66" s="48" t="n"/>
-      <c r="G66" s="48" t="n"/>
-      <c r="H66" s="48" t="n"/>
-    </row>
-    <row r="68" ht="61" customHeight="1">
-      <c r="A68" s="15" t="inlineStr">
-        <is>
-          <t>Legenda — Imp = Impatto, Prob = Probabilita, Pross = Prossimita, Vel = Velocity (1-5, 5 = peggiore; n.v. = non valutata, nessuna fonte ne documenta i tempi). Rilevanza di una fonte per la previsione: Alta = fonte primaria o caso documentato, Media = fonte specializzata, Bassa = generalista. Presidio = giudizio della Banca sui controlli, fuori dallo score. X = anni per decidere e avviare la mitigazione; Y = anni per mitigare (azioni o adeguamento strutturale); Z = anni prima che il rischio possa manifestarsi; AGIRE ORA = X + Y &gt; Z. Livello di allerta (calcolato dal registro): Attivazione = almeno due fra AGIRE ORA, KRI in rosso, notizie in peggioramento; Attenzione = uno di questi, o margine sotto l'anno con P x I alto, presidio assente o KRI in ambra; Monitoraggio = gli altri. KRI = indicatore di rischio, di esposizione (quanto la Banca e' esposta) o di evoluzione (quanto cresce il fenomeno). ◆ = tema all'attenzione del supervisore.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="C16:H16"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="E57:H57"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="C12:H12"/>
-    <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="A6:H6"/>
-    <mergeCell ref="E66:H66"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="E55:H55"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="G49:H49"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="E64:H64"/>
-    <mergeCell ref="C13:H13"/>
-    <mergeCell ref="A65:D65"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A23:H23"/>
-    <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="F58:G58"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="C15:H15"/>
-    <mergeCell ref="A49:C49"/>
-    <mergeCell ref="C14:H14"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="G50:H50"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="E59:H59"/>
-    <mergeCell ref="A68:H68"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-  </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;CUso interno&amp;RHorizon Scan NFR</oddHeader>
-    <oddFooter>&amp;L&amp;F · &amp;A&amp;RPagina &amp;P di &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
   <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10015,7 +8458,7 @@
     <row r="2" ht="34" customHeight="1">
       <c r="A2" s="17" t="inlineStr">
         <is>
-          <t>4 · NFR-02 · Concentrazione su un fornitore cloud critico</t>
+          <t>2 · NFR-02 · Concentrazione su un fornitore cloud critico</t>
         </is>
       </c>
       <c r="B2" s="18" t="n"/>
@@ -10025,7 +8468,7 @@
       <c r="F2" s="18" t="n"/>
       <c r="G2" s="19" t="inlineStr">
         <is>
-          <t>score 3,30   ● 0,00   ·   Margine 1 anno   ·   Monitoraggio</t>
+          <t>score 3,80   ▲ +0,50   ·   Margine 1 anno   ·   Attenzione</t>
         </is>
       </c>
       <c r="H2" s="18" t="n"/>
@@ -10033,7 +8476,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>L1-06 · Interruzione dell'operativita' e disfunzione dei sistemi</t>
+          <t>9.9 · Terze parti</t>
         </is>
       </c>
       <c r="B3" s="21" t="n"/>
@@ -10056,7 +8499,7 @@
       </c>
       <c r="H3" s="20" t="inlineStr">
         <is>
-          <t>Esito: Confermato · validato</t>
+          <t>Esito: Variato · validato</t>
         </is>
       </c>
     </row>
@@ -10159,8 +8602,8 @@
           <t>Probabilita</t>
         </is>
       </c>
-      <c r="B14" s="58" t="n">
-        <v>2</v>
+      <c r="B14" s="28" t="n">
+        <v>4</v>
       </c>
       <c r="C14" s="29" t="inlineStr">
         <is>
@@ -10216,7 +8659,7 @@
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>Score composito 3,30 = (0,35 x 4 + 0,25 x 2 + 0,20 x 3 + 0,20 x 4) / 1,00. La rilevanza delle fonti e' nella tabella Fonti.</t>
+          <t>Score composito 3,80 = (0,35 x 4 + 0,25 x 4 + 0,20 x 3 + 0,20 x 4) / 1,00. La rilevanza delle fonti e' nella tabella Fonti.</t>
         </is>
       </c>
     </row>
@@ -10235,9 +8678,9 @@
       <c r="H19" s="24" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
-        <is>
-          <t>Livello di allerta: Monitoraggio — nessun segnale forte.</t>
+      <c r="A20" s="56" t="inlineStr">
+        <is>
+          <t>Livello di allerta: Attenzione — KRI in rosso.</t>
         </is>
       </c>
     </row>
@@ -10265,7 +8708,7 @@
     <row r="24" ht="19.5" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>Nessun valore cambiato: confermato sulle fonti del ciclo precedente.</t>
+          <t>• Probabilita 2 → 4: Rettifica del validatore: Secondo incidente del fornitore cloud in un mese, con ripristino oltre i tempi contrattuali. (08/10/2026)</t>
         </is>
       </c>
     </row>
@@ -10324,7 +8767,7 @@
       <c r="B28" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C28" s="60" t="n">
+      <c r="C28" s="57" t="n">
         <v>2</v>
       </c>
       <c r="D28" s="35" t="n">
@@ -10346,7 +8789,7 @@
       <c r="B29" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C29" s="60" t="n">
+      <c r="C29" s="57" t="n">
         <v>2</v>
       </c>
       <c r="D29" s="35" t="n">
@@ -10368,7 +8811,7 @@
       <c r="B30" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C30" s="60" t="n">
+      <c r="C30" s="57" t="n">
         <v>2</v>
       </c>
       <c r="D30" s="35" t="n">
@@ -10390,7 +8833,7 @@
       <c r="B31" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C31" s="60" t="n">
+      <c r="C31" s="57" t="n">
         <v>2</v>
       </c>
       <c r="D31" s="35" t="n">
@@ -10412,8 +8855,8 @@
       <c r="B32" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="C32" s="60" t="n">
-        <v>2</v>
+      <c r="C32" s="36" t="n">
+        <v>4</v>
       </c>
       <c r="D32" s="35" t="n">
         <v>3</v>
@@ -10422,7 +8865,7 @@
         <v>4</v>
       </c>
       <c r="F32" s="37" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="47">
@@ -10785,7 +9228,7 @@
         </is>
       </c>
       <c r="E67" s="51" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F67" s="52" t="inlineStr">
         <is>
@@ -10795,9 +9238,9 @@
       <c r="G67" s="52" t="n">
         <v>72</v>
       </c>
-      <c r="H67" s="57" t="inlineStr">
-        <is>
-          <t>Ambra</t>
+      <c r="H67" s="53" t="inlineStr">
+        <is>
+          <t>Rosso</t>
         </is>
       </c>
     </row>
@@ -10945,6 +9388,1726 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Horizon Scan NFR — schede dei rischi · ciclo 2026Q4 · dati al 31/12/2026 · validato · Uso interno</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>3 · NFR-07 · Ransomware presso un fornitore di servizi di pagamento</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="19" t="inlineStr">
+        <is>
+          <t>score 3,75   ● 0,00   ·   Entro l'anno   ·   Attenzione</t>
+        </is>
+      </c>
+      <c r="H2" s="18" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>9.9 · Terze parti</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="n"/>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Driver: DRV-CYB, DRV-TPR</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Owner: Funzione ICT &amp; Security Risk · Presidio: Parziale</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="n"/>
+      <c r="G3" s="22" t="inlineStr">
+        <is>
+          <t>◆ Attenzione del supervisore</t>
+        </is>
+      </c>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Esito: Confermato · validato</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>Il rischio</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
+      <c r="H5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Blocco prolungato dei pagamenti per un attacco ransomware al fornitore esterno che gestisce il gateway di pagamento della Banca.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Razionale: il fenomeno in termini di rischio</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="24" t="n"/>
+      <c r="G8" s="24" t="n"/>
+      <c r="H8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="33" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>I gruppi ransomware colpiscono sempre piu' i fornitori che servono molte banche (causa); un attacco al fornitore del gateway di pagamento (evento) blocca i pagamenti della Banca finche' il fornitore non ripristina i sistemi, con danno ai clienti, sanzioni e reputazione (danno). Nessuna evidenza nuova nel trimestre: valori confermati.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>Valutazione, dimensione per dimensione (valori validati)</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>Dimensione</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Valore</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Perche' questo valore: informazioni e documenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Impatto</t>
+        </is>
+      </c>
+      <c r="B13" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Grave. Il Registro DORA classifica critico il fornitore del gateway: il blocco interrompe una funzione essenziale.</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Probabilita</t>
+        </is>
+      </c>
+      <c r="B14" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>Possibile. L'attacco ransomware a un processore di pagamenti europeo e' un caso nel settore; la Banca e' esposta perche' dipende da un solo gateway.</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>Prossimita</t>
+        </is>
+      </c>
+      <c r="B15" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Da uno a due anni. Nessun attacco o segnale specifico sul fornitore della Banca.</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="B16" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>Entro un mese. Nell'attacco al processore di pagamenti europeo i pagamenti si sono fermati il giorno stesso.</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Score composito 3,75 = (0,35 x 4 + 0,25 x 3 + 0,20 x 3 + 0,20 x 5) / 1,00. La rilevanza delle fonti e' nella tabella Fonti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>Urgenza (disuguaglianza di Mosca) e livello di allerta</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="24" t="n"/>
+      <c r="H19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="56" t="inlineStr">
+        <is>
+          <t>Livello di allerta: Attenzione — margine sotto l'anno con P x I alta, KRI in ambra o rosso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Agire entro l'anno. Tempo necessario X + Y = 0,25 + 0,50 = 0,75 anni; tempo disponibile Z = 1,5 anni (Prossimita 3). Margine Z - (X + Y) = 0,75.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>Cosa e' cambiato nel ciclo</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="24" t="n"/>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="24" t="n"/>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>Nessun valore cambiato: confermato sulle fonti del ciclo precedente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>Andamento negli ultimi trimestri</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>Ciclo</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>Imp</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>Prob</t>
+        </is>
+      </c>
+      <c r="D27" s="33" t="inlineStr">
+        <is>
+          <t>Pross</t>
+        </is>
+      </c>
+      <c r="E27" s="33" t="inlineStr">
+        <is>
+          <t>Vel</t>
+        </is>
+      </c>
+      <c r="F27" s="33" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="B28" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="37" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="B29" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F29" s="37" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B30" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C30" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F30" s="37" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="B31" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C31" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="37" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t>2026Q4</t>
+        </is>
+      </c>
+      <c r="B32" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" s="38" t="n">
+        <v>5</v>
+      </c>
+      <c r="F32" s="37" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>Fonti</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="n"/>
+      <c r="C47" s="24" t="n"/>
+      <c r="D47" s="24" t="n"/>
+      <c r="E47" s="24" t="n"/>
+      <c r="F47" s="24" t="n"/>
+      <c r="G47" s="24" t="n"/>
+      <c r="H47" s="24" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="F48" s="26" t="inlineStr">
+        <is>
+          <t>Rilevanza</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="n"/>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="39" t="inlineStr">
+        <is>
+          <t>Registro DORA: fornitore del gateway di pagamento classificato critico</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="40" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="E49" s="41" t="inlineStr">
+        <is>
+          <t>Interna</t>
+        </is>
+      </c>
+      <c r="F49" s="42" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G49" s="39" t="n"/>
+      <c r="H49" s="6" t="n"/>
+    </row>
+    <row r="50" ht="18.5" customHeight="1">
+      <c r="A50" s="39" t="inlineStr">
+        <is>
+          <t>Attacco ransomware a un processore di pagamenti europeo</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="40" t="inlineStr">
+        <is>
+          <t>20/02/2026</t>
+        </is>
+      </c>
+      <c r="E50" s="43" t="inlineStr">
+        <is>
+          <t>Esterna</t>
+        </is>
+      </c>
+      <c r="F50" s="42" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G50" s="39" t="n"/>
+      <c r="H50" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>Azioni</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="n"/>
+      <c r="C52" s="24" t="n"/>
+      <c r="D52" s="24" t="n"/>
+      <c r="E52" s="24" t="n"/>
+      <c r="F52" s="24" t="n"/>
+      <c r="G52" s="24" t="n"/>
+      <c r="H52" s="24" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="26" t="inlineStr">
+        <is>
+          <t>Azione</t>
+        </is>
+      </c>
+      <c r="F53" s="26" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H53" s="26" t="inlineStr">
+        <is>
+          <t>Orizzonte · stato</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18.5" customHeight="1">
+      <c r="A54" s="45" t="inlineStr">
+        <is>
+          <t>• Test congiunto di ripristino da ransomware con il fornitore del gateway di pagamento.</t>
+        </is>
+      </c>
+      <c r="F54" s="46" t="inlineStr">
+        <is>
+          <t>Funzione ICT &amp; Security Risk</t>
+        </is>
+      </c>
+      <c r="H54" s="46" t="inlineStr">
+        <is>
+          <t>6 mesi · Approvata (ciclo 2026Q2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="47" t="inlineStr">
+        <is>
+          <t>Perche': Il ripristino da ransomware non e' mai stato testato con il fornitore.</t>
+        </is>
+      </c>
+      <c r="B55" s="48" t="n"/>
+      <c r="C55" s="48" t="n"/>
+      <c r="D55" s="48" t="n"/>
+      <c r="E55" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: non indicato nel razionale di A1.</t>
+        </is>
+      </c>
+      <c r="F55" s="48" t="n"/>
+      <c r="G55" s="48" t="n"/>
+      <c r="H55" s="48" t="n"/>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="45" t="inlineStr">
+        <is>
+          <t>• Inserire nel contratto con il fornitore del gateway di pagamento tempi di ripristino garantiti dopo un attacco ransomware, con penali.</t>
+        </is>
+      </c>
+      <c r="F56" s="46" t="inlineStr">
+        <is>
+          <t>Funzione ICT &amp; Security Risk</t>
+        </is>
+      </c>
+      <c r="H56" s="46" t="inlineStr">
+        <is>
+          <t>6 mesi · Approvata (ciclo 2026Q3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="47" t="inlineStr">
+        <is>
+          <t>Perche': Il test congiunto di ripristino (2026Q2-NFR-07-A1) misura i tempi; il contratto li rende vincolanti per il fornitore.</t>
+        </is>
+      </c>
+      <c r="B57" s="48" t="n"/>
+      <c r="C57" s="48" t="n"/>
+      <c r="D57" s="48" t="n"/>
+      <c r="E57" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: non indicato nel razionale di A1.</t>
+        </is>
+      </c>
+      <c r="F57" s="48" t="n"/>
+      <c r="G57" s="48" t="n"/>
+      <c r="H57" s="48" t="n"/>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="45" t="inlineStr">
+        <is>
+          <t>• Prevedere un canale di pagamento alternativo, attivabile entro 24 ore, se il gateway del fornitore resta bloccato da un attacco.</t>
+        </is>
+      </c>
+      <c r="F58" s="46" t="inlineStr">
+        <is>
+          <t>Funzione ICT &amp; Security Risk</t>
+        </is>
+      </c>
+      <c r="H58" s="46" t="inlineStr">
+        <is>
+          <t>6 mesi · Approvata (ciclo 2026Q4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="32" customHeight="1">
+      <c r="A59" s="47" t="inlineStr">
+        <is>
+          <t>Perche': Il test di ripristino (2026Q2-NFR-07-A1) e i tempi contrattuali (2026Q3-NFR-07-A1) non coprono un blocco lungo del fornitore: serve un'alternativa.</t>
+        </is>
+      </c>
+      <c r="B59" s="48" t="n"/>
+      <c r="C59" s="48" t="n"/>
+      <c r="D59" s="48" t="n"/>
+      <c r="E59" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: Un blocco del fornitore non ferma i pagamenti per piu' di un giorno, quindi un danno contenuto anche nel caso peggiore.</t>
+        </is>
+      </c>
+      <c r="F59" s="48" t="n"/>
+      <c r="G59" s="48" t="n"/>
+      <c r="H59" s="48" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>KRI in vigore</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="n"/>
+      <c r="C61" s="24" t="n"/>
+      <c r="D61" s="24" t="n"/>
+      <c r="E61" s="24" t="n"/>
+      <c r="F61" s="24" t="n"/>
+      <c r="G61" s="24" t="n"/>
+      <c r="H61" s="24" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="49" t="inlineStr">
+        <is>
+          <t>Indicatore</t>
+        </is>
+      </c>
+      <c r="E62" s="49" t="inlineStr">
+        <is>
+          <t>Valore</t>
+        </is>
+      </c>
+      <c r="F62" s="49" t="inlineStr">
+        <is>
+          <t>Soglie (attenzione / allerta)</t>
+        </is>
+      </c>
+      <c r="G62" s="49" t="inlineStr">
+        <is>
+          <t>Ciclo prima</t>
+        </is>
+      </c>
+      <c r="H62" s="49" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="50" t="inlineStr">
+        <is>
+          <t>[Esposizione] Fornitori di pagamento critici senza test di ripristino da ransomware (n)</t>
+        </is>
+      </c>
+      <c r="E63" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="52" t="inlineStr">
+        <is>
+          <t>1,0 / 2,0</t>
+        </is>
+      </c>
+      <c r="G63" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H63" s="58" t="inlineStr">
+        <is>
+          <t>Ambra</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="47" t="inlineStr">
+        <is>
+          <t>Perche' lo misuriamo: Misura quanto la Banca e' esposta: un fornitore critico mai provato nel ripristino e' un blocco di durata sconosciuta.</t>
+        </is>
+      </c>
+      <c r="B64" s="48" t="n"/>
+      <c r="C64" s="48" t="n"/>
+      <c r="D64" s="48" t="n"/>
+      <c r="E64" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: Atteso a zero dopo il test congiunto; ogni nuovo fornitore critico senza test lo riporta in ambra.</t>
+        </is>
+      </c>
+      <c r="F64" s="48" t="n"/>
+      <c r="G64" s="48" t="n"/>
+      <c r="H64" s="48" t="n"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="50" t="inlineStr">
+        <is>
+          <t>[Evoluzione] Ore di indisponibilita' del gateway di pagamento nel trimestre (ore)</t>
+        </is>
+      </c>
+      <c r="E65" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F65" s="52" t="inlineStr">
+        <is>
+          <t>4,0 / 12,0</t>
+        </is>
+      </c>
+      <c r="G65" s="52" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H65" s="54" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="47" t="inlineStr">
+        <is>
+          <t>Perche' lo misuriamo: Misura le interruzioni reali del gateway, il canale attraverso cui il rischio colpisce.</t>
+        </is>
+      </c>
+      <c r="B66" s="48" t="n"/>
+      <c r="C66" s="48" t="n"/>
+      <c r="D66" s="48" t="n"/>
+      <c r="E66" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: Poche ore e stabili; oltre la soglia di allerta il fornitore ha problemi di continuita' e la Prossimita' va rivista.</t>
+        </is>
+      </c>
+      <c r="F66" s="48" t="n"/>
+      <c r="G66" s="48" t="n"/>
+      <c r="H66" s="48" t="n"/>
+    </row>
+    <row r="68" ht="61" customHeight="1">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>Legenda — Imp = Impatto, Prob = Probabilita, Pross = Prossimita, Vel = Velocity (1-5, 5 = peggiore; n.v. = non valutata, nessuna fonte ne documenta i tempi). Rilevanza di una fonte per la previsione: Alta = fonte primaria o caso documentato, Media = fonte specializzata, Bassa = generalista. Presidio = giudizio della Banca sui controlli, fuori dallo score. X = anni per decidere e avviare la mitigazione; Y = anni per mitigare (azioni o adeguamento strutturale); Z = anni prima che il rischio possa manifestarsi; AGIRE ORA = X + Y &gt; Z. Livello di allerta (calcolato dal registro): Attivazione = almeno due fra AGIRE ORA, KRI in rosso, notizie in peggioramento; Attenzione = uno di questi, o margine sotto l'anno con P x I alto, presidio assente o KRI in ambra; Monitoraggio = gli altri. KRI = indicatore di rischio, di esposizione (quanto la Banca e' esposta) o di evoluzione (quanto cresce il fenomeno). ◆ = tema all'attenzione del supervisore.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="51">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;CUso interno&amp;RHorizon Scan NFR</oddHeader>
+    <oddFooter>&amp;L&amp;F · &amp;A&amp;RPagina &amp;P di &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Horizon Scan NFR — schede dei rischi · ciclo 2026Q4 · dati al 31/12/2026 · validato · Uso interno</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="34" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>4 · NFR-12 · Errori operativi nei pagamenti istantanei obbligatori</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="n"/>
+      <c r="C2" s="18" t="n"/>
+      <c r="D2" s="18" t="n"/>
+      <c r="E2" s="18" t="n"/>
+      <c r="F2" s="18" t="n"/>
+      <c r="G2" s="19" t="inlineStr">
+        <is>
+          <t>score 3,65   ● 0,00   ·   Entro l'anno   ·   Attenzione</t>
+        </is>
+      </c>
+      <c r="H2" s="18" t="n"/>
+    </row>
+    <row r="3" ht="28" customHeight="1">
+      <c r="A3" s="20" t="inlineStr">
+        <is>
+          <t>9.13 · Processo</t>
+        </is>
+      </c>
+      <c r="B3" s="21" t="n"/>
+      <c r="C3" s="20" t="inlineStr">
+        <is>
+          <t>Driver: DRV-TEC</t>
+        </is>
+      </c>
+      <c r="D3" s="21" t="n"/>
+      <c r="E3" s="20" t="inlineStr">
+        <is>
+          <t>Owner: Funzione Operations · Presidio: Parziale</t>
+        </is>
+      </c>
+      <c r="F3" s="21" t="n"/>
+      <c r="G3" s="20" t="n"/>
+      <c r="H3" s="20" t="inlineStr">
+        <is>
+          <t>Esito: Confermato · validato</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>Il rischio</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+      <c r="D5" s="24" t="n"/>
+      <c r="E5" s="24" t="n"/>
+      <c r="F5" s="24" t="n"/>
+      <c r="G5" s="24" t="n"/>
+      <c r="H5" s="24" t="n"/>
+    </row>
+    <row r="6" ht="19.5" customHeight="1">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Errori di riconciliazione e rimborsi indebiti dopo l'obbligo di offrire i bonifici istantanei a tutta la clientela.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Razionale: il fenomeno in termini di rischio</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="24" t="n"/>
+      <c r="D8" s="24" t="n"/>
+      <c r="E8" s="24" t="n"/>
+      <c r="F8" s="24" t="n"/>
+      <c r="G8" s="24" t="n"/>
+      <c r="H8" s="24" t="n"/>
+    </row>
+    <row r="9" ht="33" customHeight="1">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>L'obbligo di offrire i bonifici istantanei a tutta la clientela moltiplica i volumi da riconciliare in tempo reale (causa); differenze di riconciliazione non risolte ed eccezioni portano a rimborsi indebiti o pagamenti errati (evento); la Banca subisce perdite operative e reclami (danno). Nessuna evidenza nuova nel trimestre: valori confermati.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>Valutazione, dimensione per dimensione (valori validati)</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="24" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>Dimensione</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>Valore</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>Perche' questo valore: informazioni e documenti</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="33" customHeight="1">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Impatto</t>
+        </is>
+      </c>
+      <c r="B13" s="55" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>Rilevante. Il Piano di adeguamento al regolamento sui bonifici istantanei estende il servizio a tutta la clientela: un errore tocca una clientela ampia.</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>Probabilita</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>Probabile. Il Report operativo dei pagamenti istantanei di maggio documenta differenze di riconciliazione in crescita presso la Banca.</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="27" t="inlineStr">
+        <is>
+          <t>Prossimita</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C15" s="29" t="inlineStr">
+        <is>
+          <t>Entro dodici mesi. Le differenze aperte del Report operativo sono quasi-incidenti gia' documentati presso la Banca.</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="27" t="inlineStr">
+        <is>
+          <t>Velocity</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="29" t="inlineStr">
+        <is>
+          <t>Da uno a tre mesi. Con la riconciliazione settimanale le differenze si accumulano in poche settimane (Report operativo).</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="31" t="inlineStr">
+        <is>
+          <t>Score composito 3,65 = (0,35 x 3 + 0,25 x 4 + 0,20 x 4 + 0,20 x 4) / 1,00. La rilevanza delle fonti e' nella tabella Fonti.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>Urgenza (disuguaglianza di Mosca) e livello di allerta</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="24" t="n"/>
+      <c r="H19" s="24" t="n"/>
+    </row>
+    <row r="20" ht="19.5" customHeight="1">
+      <c r="A20" s="56" t="inlineStr">
+        <is>
+          <t>Livello di allerta: Attenzione — margine sotto l'anno con P x I alta, KRI in ambra o rosso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="19.5" customHeight="1">
+      <c r="A21" s="25" t="inlineStr">
+        <is>
+          <t>Agire entro l'anno. Tempo necessario X + Y = 0,25 + 0,25 = 0,50 anni; tempo disponibile Z = 0,5 anni (Prossimita 4). Margine Z - (X + Y) = 0,00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>Cosa e' cambiato nel ciclo</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="24" t="n"/>
+      <c r="F23" s="24" t="n"/>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="24" t="n"/>
+    </row>
+    <row r="24" ht="19.5" customHeight="1">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
+          <t>Nessun valore cambiato: confermato sulle fonti del ciclo precedente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>Andamento negli ultimi trimestri</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>Ciclo</t>
+        </is>
+      </c>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>Imp</t>
+        </is>
+      </c>
+      <c r="C27" s="33" t="inlineStr">
+        <is>
+          <t>Prob</t>
+        </is>
+      </c>
+      <c r="D27" s="33" t="inlineStr">
+        <is>
+          <t>Pross</t>
+        </is>
+      </c>
+      <c r="E27" s="33" t="inlineStr">
+        <is>
+          <t>Vel</t>
+        </is>
+      </c>
+      <c r="F27" s="33" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="34" t="inlineStr">
+        <is>
+          <t>2025Q4</t>
+        </is>
+      </c>
+      <c r="B28" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="37" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="34" t="inlineStr">
+        <is>
+          <t>2026Q1</t>
+        </is>
+      </c>
+      <c r="B29" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C29" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="37" t="n">
+        <v>3.45</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="34" t="inlineStr">
+        <is>
+          <t>2026Q2</t>
+        </is>
+      </c>
+      <c r="B30" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E30" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" s="37" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="34" t="inlineStr">
+        <is>
+          <t>2026Q3</t>
+        </is>
+      </c>
+      <c r="B31" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C31" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="37" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t>2026Q4</t>
+        </is>
+      </c>
+      <c r="B32" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" s="37" t="n">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="inlineStr">
+        <is>
+          <t>Fonti</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="n"/>
+      <c r="C47" s="24" t="n"/>
+      <c r="D47" s="24" t="n"/>
+      <c r="E47" s="24" t="n"/>
+      <c r="F47" s="24" t="n"/>
+      <c r="G47" s="24" t="n"/>
+      <c r="H47" s="24" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="inlineStr">
+        <is>
+          <t>Fonte</t>
+        </is>
+      </c>
+      <c r="D48" s="26" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="E48" s="26" t="inlineStr">
+        <is>
+          <t>Tipo</t>
+        </is>
+      </c>
+      <c r="F48" s="26" t="inlineStr">
+        <is>
+          <t>Rilevanza</t>
+        </is>
+      </c>
+      <c r="G48" s="26" t="n"/>
+    </row>
+    <row r="49" ht="32" customHeight="1">
+      <c r="A49" s="39" t="inlineStr">
+        <is>
+          <t>Piano di adeguamento al regolamento sui bonifici istantanei</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="40" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="E49" s="41" t="inlineStr">
+        <is>
+          <t>Interna</t>
+        </is>
+      </c>
+      <c r="F49" s="42" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G49" s="39" t="n"/>
+      <c r="H49" s="6" t="n"/>
+    </row>
+    <row r="50" ht="18.5" customHeight="1">
+      <c r="A50" s="39" t="inlineStr">
+        <is>
+          <t>Report operativo dei pagamenti istantanei — maggio</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="40" t="inlineStr">
+        <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="E50" s="41" t="inlineStr">
+        <is>
+          <t>Interna</t>
+        </is>
+      </c>
+      <c r="F50" s="42" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="G50" s="39" t="n"/>
+      <c r="H50" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="23" t="inlineStr">
+        <is>
+          <t>Azioni</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="n"/>
+      <c r="C52" s="24" t="n"/>
+      <c r="D52" s="24" t="n"/>
+      <c r="E52" s="24" t="n"/>
+      <c r="F52" s="24" t="n"/>
+      <c r="G52" s="24" t="n"/>
+      <c r="H52" s="24" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="26" t="inlineStr">
+        <is>
+          <t>Azione</t>
+        </is>
+      </c>
+      <c r="F53" s="26" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="H53" s="26" t="inlineStr">
+        <is>
+          <t>Orizzonte · stato</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18.5" customHeight="1">
+      <c r="A54" s="45" t="inlineStr">
+        <is>
+          <t>• Controllo giornaliero automatico delle differenze di riconciliazione sui bonifici istantanei.</t>
+        </is>
+      </c>
+      <c r="F54" s="46" t="inlineStr">
+        <is>
+          <t>Funzione Operations</t>
+        </is>
+      </c>
+      <c r="H54" s="46" t="inlineStr">
+        <is>
+          <t>3 mesi · Approvata (ciclo 2026Q2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="47" t="inlineStr">
+        <is>
+          <t>Perche': La riconciliazione oggi e' settimanale: gli errori emergono troppo tardi.</t>
+        </is>
+      </c>
+      <c r="B55" s="48" t="n"/>
+      <c r="C55" s="48" t="n"/>
+      <c r="D55" s="48" t="n"/>
+      <c r="E55" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: non indicato nel razionale di A1.</t>
+        </is>
+      </c>
+      <c r="F55" s="48" t="n"/>
+      <c r="G55" s="48" t="n"/>
+      <c r="H55" s="48" t="n"/>
+    </row>
+    <row r="56" ht="32" customHeight="1">
+      <c r="A56" s="45" t="inlineStr">
+        <is>
+          <t>• Avvisare in automatico il responsabile delle operazioni di ogni differenza di riconciliazione sui bonifici istantanei aperta a fine giornata.</t>
+        </is>
+      </c>
+      <c r="F56" s="46" t="inlineStr">
+        <is>
+          <t>Funzione Operations</t>
+        </is>
+      </c>
+      <c r="H56" s="46" t="inlineStr">
+        <is>
+          <t>3 mesi · Approvata (ciclo 2026Q3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="32" customHeight="1">
+      <c r="A57" s="47" t="inlineStr">
+        <is>
+          <t>Perche': Il controllo giornaliero (2026Q2-NFR-12-A1) trova le differenze; l'avviso porta a chi decide quelle non chiuse in giornata.</t>
+        </is>
+      </c>
+      <c r="B57" s="48" t="n"/>
+      <c r="C57" s="48" t="n"/>
+      <c r="D57" s="48" t="n"/>
+      <c r="E57" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: non indicato nel razionale di A1.</t>
+        </is>
+      </c>
+      <c r="F57" s="48" t="n"/>
+      <c r="G57" s="48" t="n"/>
+      <c r="H57" s="48" t="n"/>
+    </row>
+    <row r="58" ht="32" customHeight="1">
+      <c r="A58" s="45" t="inlineStr">
+        <is>
+          <t>• Introdurre un test di riconciliazione su dati anonimizzati prima di ogni rilascio del motore dei bonifici istantanei.</t>
+        </is>
+      </c>
+      <c r="F58" s="46" t="inlineStr">
+        <is>
+          <t>Funzione Operations</t>
+        </is>
+      </c>
+      <c r="H58" s="46" t="inlineStr">
+        <is>
+          <t>3 mesi · Approvata (ciclo 2026Q4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="47" t="inlineStr">
+        <is>
+          <t>Perche': Il controllo giornaliero (2026Q2-NFR-12-A1) e l'avviso (2026Q3-NFR-12-A1) trovano le differenze dopo; molte nascono dalle modifiche al software, che il test ferma prima.</t>
+        </is>
+      </c>
+      <c r="B59" s="48" t="n"/>
+      <c r="C59" s="48" t="n"/>
+      <c r="D59" s="48" t="n"/>
+      <c r="E59" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: Meno differenze dopo i rilasci; quelle aperte oltre un giorno (NFR-12-K1) scendono sotto la soglia di attenzione.</t>
+        </is>
+      </c>
+      <c r="F59" s="48" t="n"/>
+      <c r="G59" s="48" t="n"/>
+      <c r="H59" s="48" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="23" t="inlineStr">
+        <is>
+          <t>KRI in vigore</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="n"/>
+      <c r="C61" s="24" t="n"/>
+      <c r="D61" s="24" t="n"/>
+      <c r="E61" s="24" t="n"/>
+      <c r="F61" s="24" t="n"/>
+      <c r="G61" s="24" t="n"/>
+      <c r="H61" s="24" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="49" t="inlineStr">
+        <is>
+          <t>Indicatore</t>
+        </is>
+      </c>
+      <c r="E62" s="49" t="inlineStr">
+        <is>
+          <t>Valore</t>
+        </is>
+      </c>
+      <c r="F62" s="49" t="inlineStr">
+        <is>
+          <t>Soglie (attenzione / allerta)</t>
+        </is>
+      </c>
+      <c r="G62" s="49" t="inlineStr">
+        <is>
+          <t>Ciclo prima</t>
+        </is>
+      </c>
+      <c r="H62" s="49" t="inlineStr">
+        <is>
+          <t>Stato</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="50" t="inlineStr">
+        <is>
+          <t>[Evoluzione] Differenze di riconciliazione sui bonifici istantanei aperte oltre 1 giorno (n)</t>
+        </is>
+      </c>
+      <c r="E63" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="F63" s="52" t="inlineStr">
+        <is>
+          <t>10,0 / 30,0</t>
+        </is>
+      </c>
+      <c r="G63" s="52" t="n">
+        <v>12</v>
+      </c>
+      <c r="H63" s="54" t="inlineStr">
+        <is>
+          <t>Verde</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="47" t="inlineStr">
+        <is>
+          <t>Perche' lo misuriamo: Misura il fenomeno nel punto in cui produce perdite: le differenze che non si chiudono in giornata.</t>
+        </is>
+      </c>
+      <c r="B64" s="48" t="n"/>
+      <c r="C64" s="48" t="n"/>
+      <c r="D64" s="48" t="n"/>
+      <c r="E64" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: In calo con il controllo giornaliero; oltre la soglia di allerta la riconciliazione non regge i volumi.</t>
+        </is>
+      </c>
+      <c r="F64" s="48" t="n"/>
+      <c r="G64" s="48" t="n"/>
+      <c r="H64" s="48" t="n"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="50" t="inlineStr">
+        <is>
+          <t>[Esposizione] Tempo medio di risoluzione delle eccezioni sui pagamenti istantanei (ore)</t>
+        </is>
+      </c>
+      <c r="E65" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="F65" s="52" t="inlineStr">
+        <is>
+          <t>4,0 / 12,0</t>
+        </is>
+      </c>
+      <c r="G65" s="52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H65" s="58" t="inlineStr">
+        <is>
+          <t>Ambra</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="47" t="inlineStr">
+        <is>
+          <t>Perche' lo misuriamo: Misura quanto a lungo la Banca resta esposta a un'eccezione aperta.</t>
+        </is>
+      </c>
+      <c r="B66" s="48" t="n"/>
+      <c r="C66" s="48" t="n"/>
+      <c r="D66" s="48" t="n"/>
+      <c r="E66" s="47" t="inlineStr">
+        <is>
+          <t>Effetto atteso: Sotto la soglia di attenzione quando il controllo giornaliero e' a regime.</t>
+        </is>
+      </c>
+      <c r="F66" s="48" t="n"/>
+      <c r="G66" s="48" t="n"/>
+      <c r="H66" s="48" t="n"/>
+    </row>
+    <row r="68" ht="61" customHeight="1">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>Legenda — Imp = Impatto, Prob = Probabilita, Pross = Prossimita, Vel = Velocity (1-5, 5 = peggiore; n.v. = non valutata, nessuna fonte ne documenta i tempi). Rilevanza di una fonte per la previsione: Alta = fonte primaria o caso documentato, Media = fonte specializzata, Bassa = generalista. Presidio = giudizio della Banca sui controlli, fuori dallo score. X = anni per decidere e avviare la mitigazione; Y = anni per mitigare (azioni o adeguamento strutturale); Z = anni prima che il rischio possa manifestarsi; AGIRE ORA = X + Y &gt; Z. Livello di allerta (calcolato dal registro): Attivazione = almeno due fra AGIRE ORA, KRI in rosso, notizie in peggioramento; Attenzione = uno di questi, o margine sotto l'anno con P x I alto, presidio assente o KRI in ambra; Monitoraggio = gli altri. KRI = indicatore di rischio, di esposizione (quanto la Banca e' esposta) o di evoluzione (quanto cresce il fenomeno). ◆ = tema all'attenzione del supervisore.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="51">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="E57:H57"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="A61:H61"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="E66:H66"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="E55:H55"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="G49:H49"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="E64:H64"/>
+    <mergeCell ref="C13:H13"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="C15:H15"/>
+    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="C14:H14"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="G50:H50"/>
+    <mergeCell ref="A57:D57"/>
+    <mergeCell ref="E59:H59"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;CUso interno&amp;RHorizon Scan NFR</oddHeader>
+    <oddFooter>&amp;L&amp;F · &amp;A&amp;RPagina &amp;P di &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -10992,7 +11155,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>L1-04 · Clientela, prodotti e prassi professionali</t>
+          <t>9.1 · Condotta</t>
         </is>
       </c>
       <c r="B3" s="21" t="n"/>
@@ -11154,7 +11317,7 @@
           <t>Velocity</t>
         </is>
       </c>
-      <c r="B16" s="58" t="n">
+      <c r="B16" s="59" t="n">
         <v>2</v>
       </c>
       <c r="C16" s="29" t="inlineStr">
@@ -11285,7 +11448,7 @@
       <c r="D28" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="E28" s="60" t="n">
+      <c r="E28" s="57" t="n">
         <v>2</v>
       </c>
       <c r="F28" s="37" t="n">
@@ -11307,7 +11470,7 @@
       <c r="D29" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="E29" s="60" t="n">
+      <c r="E29" s="57" t="n">
         <v>2</v>
       </c>
       <c r="F29" s="37" t="n">
@@ -11329,7 +11492,7 @@
       <c r="D30" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="60" t="n">
+      <c r="E30" s="57" t="n">
         <v>2</v>
       </c>
       <c r="F30" s="37" t="n">
@@ -11351,7 +11514,7 @@
       <c r="D31" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="60" t="n">
+      <c r="E31" s="57" t="n">
         <v>2</v>
       </c>
       <c r="F31" s="37" t="n">
@@ -11373,7 +11536,7 @@
       <c r="D32" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="E32" s="60" t="n">
+      <c r="E32" s="57" t="n">
         <v>2</v>
       </c>
       <c r="F32" s="37" t="n">
@@ -11689,7 +11852,7 @@
       <c r="G64" s="52" t="n">
         <v>1.9</v>
       </c>
-      <c r="H64" s="57" t="inlineStr">
+      <c r="H64" s="58" t="inlineStr">
         <is>
           <t>Ambra</t>
         </is>
@@ -11732,7 +11895,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="H66" s="57" t="inlineStr">
+      <c r="H66" s="58" t="inlineStr">
         <is>
           <t>Ambra</t>
         </is>
@@ -11880,7 +12043,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>L1-07 · Esecuzione, consegna e gestione dei processi</t>
+          <t>9.13 · Processo</t>
         </is>
       </c>
       <c r="B3" s="21" t="n"/>
@@ -12078,7 +12241,7 @@
       <c r="H19" s="24" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>Livello di allerta: Monitoraggio — nessun segnale forte.</t>
         </is>
@@ -12727,7 +12890,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>L1-01 · Frode interna</t>
+          <t>9.7 · Sicurezza informatica</t>
         </is>
       </c>
       <c r="B3" s="21" t="n"/>
@@ -13630,7 +13793,7 @@
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="20" t="inlineStr">
         <is>
-          <t>L1-04 · Clientela, prodotti e prassi professionali</t>
+          <t>9.1 · Condotta</t>
         </is>
       </c>
       <c r="B3" s="21" t="n"/>
@@ -13828,7 +13991,7 @@
       <c r="H19" s="24" t="n"/>
     </row>
     <row r="20" ht="19.5" customHeight="1">
-      <c r="A20" s="59" t="inlineStr">
+      <c r="A20" s="60" t="inlineStr">
         <is>
           <t>Livello di allerta: Monitoraggio — nessun segnale forte.</t>
         </is>
@@ -14283,7 +14446,7 @@
       <c r="G62" s="52" t="n">
         <v>1.9</v>
       </c>
-      <c r="H62" s="57" t="inlineStr">
+      <c r="H62" s="58" t="inlineStr">
         <is>
           <t>Ambra</t>
         </is>
@@ -14324,7 +14487,7 @@
       <c r="G64" s="52" t="n">
         <v>45</v>
       </c>
-      <c r="H64" s="57" t="inlineStr">
+      <c r="H64" s="58" t="inlineStr">
         <is>
           <t>Ambra</t>
         </is>
